--- a/Stock_OneClick/history/scan_result_20260603_194337.xlsx
+++ b/Stock_OneClick/history/scan_result_20260603_194337.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q252"/>
+  <dimension ref="A1:Q251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -670,24 +670,12 @@
       <c r="J3" s="4" t="n">
         <v>184.07</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-03; 相对D0=1.42%; 本次触发=2026-06-03(预警买入); 历史重复3次; 重复日期=2026-05-27, 2026-06-01, 2026-06-03</t>
@@ -739,24 +727,6 @@
       <c r="J4" t="n">
         <v>50.01</v>
       </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>D0=50.66; 最新=2026-06-03; 相对D0=-1.28%; 本次触发=2026-06-03(预警买入); 历史重复3次; 重复日期=2026-05-27, 2026-06-01, 2026-06-03</t>
@@ -808,24 +778,6 @@
       <c r="J5" t="n">
         <v>622.98</v>
       </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>D0=610.26; 最新=2026-06-03; 相对D0=2.08%; 本次触发=2026-06-03(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-03</t>
@@ -877,24 +829,6 @@
       <c r="J6" t="n">
         <v>23.3</v>
       </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-03; 相对D0=3.51%; 本次触发=2026-06-03(预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-06-02, 2026-06-03</t>
@@ -946,24 +880,6 @@
       <c r="J7" t="n">
         <v>146.47</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-03; 相对D0=12.24%; 本次触发=2026-06-03(预警买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1015,24 +931,6 @@
       <c r="J8" t="n">
         <v>377</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=388.47; 最新=2026-06-03; 相对D0=-2.95%; 本次触发=2026-06-03(预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-03</t>
@@ -1084,24 +982,12 @@
       <c r="J9" s="4" t="n">
         <v>119.05</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-03; 相对D0=3.00%; 本次触发=2026-06-03(正式买入); 历史重复2次; 重复日期=2026-06-02, 2026-06-03</t>
@@ -1153,24 +1039,6 @@
       <c r="J10" t="n">
         <v>68.81</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-03; 相对D0=-1.09%; 本次触发=2026-06-03(预警买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1222,24 +1090,6 @@
       <c r="J11" t="n">
         <v>310.26</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=315.20; 最新=2026-06-03; 相对D0=-1.57%; 本次触发=2026-06-03(预警买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1291,24 +1141,12 @@
       <c r="J12" s="4" t="n">
         <v>41.03</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>D0=40.13; 最新=2026-06-03; 相对D0=2.24%; 本次触发=2026-06-03(正式买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1360,24 +1198,12 @@
       <c r="J13" s="4" t="n">
         <v>30.84</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=25.86; 最新=2026-06-03; 相对D0=19.26%; 本次触发=2026-06-03(预警买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1429,24 +1255,6 @@
       <c r="J14" t="n">
         <v>498.02</v>
       </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>D0=508.35; 最新=2026-06-03; 相对D0=-2.03%; 本次触发=2026-06-03(预警买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1498,24 +1306,12 @@
       <c r="J15" s="4" t="n">
         <v>267.91</v>
       </c>
-      <c r="K15" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O15" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>D0=274.71; 最新=2026-06-03; 相对D0=-2.48%; 本次触发=2026-06-03(预警买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1567,27 +1363,15 @@
       <c r="J16" s="4" t="n">
         <v>58.71</v>
       </c>
-      <c r="K16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P16" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>D0=57.96; 最新=2026-06-03; 相对D0=1.29%; 本次触发=2026-06-03(第一买入点); 历史重复1次; 重复日期=2026-06-03</t>
+          <t>D0=57.96; 最新=2026-06-03; 相对D0=1.29%; 本次触发=2026-06-03(第一观察点); 历史重复1次; 重复日期=2026-06-03</t>
         </is>
       </c>
     </row>
@@ -1636,24 +1420,12 @@
       <c r="J17" s="4" t="n">
         <v>184.07</v>
       </c>
-      <c r="K17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>D0=184.07; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1705,24 +1477,6 @@
       <c r="J18" t="n">
         <v>310.26</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=310.26; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1774,24 +1528,6 @@
       <c r="J19" t="n">
         <v>282.27</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=282.27; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1843,24 +1579,6 @@
       <c r="J20" t="n">
         <v>116.6</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=116.60; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1912,24 +1630,12 @@
       <c r="J21" s="4" t="n">
         <v>119.05</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=119.05; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入)</t>
@@ -1981,24 +1687,6 @@
       <c r="J22" t="n">
         <v>121.04</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=121.04; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2050,24 +1738,12 @@
       <c r="J23" s="4" t="n">
         <v>41.03</v>
       </c>
-      <c r="K23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>D0=41.03; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入)</t>
@@ -2119,24 +1795,6 @@
       <c r="J24" t="n">
         <v>50.01</v>
       </c>
-      <c r="K24" t="n">
-        <v/>
-      </c>
-      <c r="L24" t="n">
-        <v/>
-      </c>
-      <c r="M24" t="n">
-        <v/>
-      </c>
-      <c r="N24" t="n">
-        <v/>
-      </c>
-      <c r="O24" t="n">
-        <v/>
-      </c>
-      <c r="P24" t="n">
-        <v/>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>D0=50.01; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2188,24 +1846,6 @@
       <c r="J25" t="n">
         <v>507.57</v>
       </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
-      <c r="L25" t="n">
-        <v/>
-      </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
-      <c r="O25" t="n">
-        <v/>
-      </c>
-      <c r="P25" t="n">
-        <v/>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>D0=507.57; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -2257,24 +1897,6 @@
       <c r="J26" t="n">
         <v>622.98</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=622.98; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -2326,24 +1948,6 @@
       <c r="J27" t="n">
         <v>80.14</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>D0=80.14; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2395,24 +1999,6 @@
       <c r="J28" t="n">
         <v>23.3</v>
       </c>
-      <c r="K28" t="n">
-        <v/>
-      </c>
-      <c r="L28" t="n">
-        <v/>
-      </c>
-      <c r="M28" t="n">
-        <v/>
-      </c>
-      <c r="N28" t="n">
-        <v/>
-      </c>
-      <c r="O28" t="n">
-        <v/>
-      </c>
-      <c r="P28" t="n">
-        <v/>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>D0=23.30; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2464,24 +2050,6 @@
       <c r="J29" t="n">
         <v>68.81</v>
       </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
-      <c r="L29" t="n">
-        <v/>
-      </c>
-      <c r="M29" t="n">
-        <v/>
-      </c>
-      <c r="N29" t="n">
-        <v/>
-      </c>
-      <c r="O29" t="n">
-        <v/>
-      </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>D0=68.81; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2533,24 +2101,12 @@
       <c r="J30" s="4" t="n">
         <v>30.84</v>
       </c>
-      <c r="K30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>D0=30.84; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2602,24 +2158,6 @@
       <c r="J31" t="n">
         <v>146.47</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=146.47; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2671,24 +2209,6 @@
       <c r="J32" t="n">
         <v>498.02</v>
       </c>
-      <c r="K32" t="n">
-        <v/>
-      </c>
-      <c r="L32" t="n">
-        <v/>
-      </c>
-      <c r="M32" t="n">
-        <v/>
-      </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
-      <c r="O32" t="n">
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>D0=498.02; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2740,24 +2260,6 @@
       <c r="J33" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="K33" t="n">
-        <v/>
-      </c>
-      <c r="L33" t="n">
-        <v/>
-      </c>
-      <c r="M33" t="n">
-        <v/>
-      </c>
-      <c r="N33" t="n">
-        <v/>
-      </c>
-      <c r="O33" t="n">
-        <v/>
-      </c>
-      <c r="P33" t="n">
-        <v/>
-      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>D0=90.49; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2809,24 +2311,12 @@
       <c r="J34" s="4" t="n">
         <v>267.91</v>
       </c>
-      <c r="K34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P34" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>D0=267.91; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2878,24 +2368,6 @@
       <c r="J35" t="n">
         <v>377</v>
       </c>
-      <c r="K35" t="n">
-        <v/>
-      </c>
-      <c r="L35" t="n">
-        <v/>
-      </c>
-      <c r="M35" t="n">
-        <v/>
-      </c>
-      <c r="N35" t="n">
-        <v/>
-      </c>
-      <c r="O35" t="n">
-        <v/>
-      </c>
-      <c r="P35" t="n">
-        <v/>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>D0=377.00; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2947,27 +2419,15 @@
       <c r="J36" s="4" t="n">
         <v>58.71</v>
       </c>
-      <c r="K36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O36" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4" t="n"/>
+      <c r="O36" s="4" t="n"/>
+      <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="inlineStr">
         <is>
-          <t>D0=58.71; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(第一买入点)</t>
+          <t>D0=58.71; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -3016,24 +2476,12 @@
       <c r="J37" s="4" t="n">
         <v>184.72</v>
       </c>
-      <c r="K37" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
       <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-03; 相对D0=-8.96%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -3085,24 +2533,12 @@
       <c r="J38" s="4" t="n">
         <v>183.45</v>
       </c>
-      <c r="K38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="n"/>
+      <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-03; 相对D0=9.61%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -3154,24 +2590,12 @@
       <c r="J39" s="4" t="n">
         <v>267.24</v>
       </c>
-      <c r="K39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
+      <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>D0=294.07; 最新=2026-06-03; 相对D0=-9.12%; 历史重复1次; 重复日期=2026-05-29</t>
@@ -3223,24 +2647,12 @@
       <c r="J40" s="4" t="n">
         <v>56.12</v>
       </c>
-      <c r="K40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-03; 相对D0=20.61%</t>
@@ -3292,24 +2704,6 @@
       <c r="J41" t="n">
         <v>16.42</v>
       </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-03; 相对D0=1.86%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -3361,24 +2755,6 @@
       <c r="J42" t="n">
         <v>190.61</v>
       </c>
-      <c r="K42" t="n">
-        <v/>
-      </c>
-      <c r="L42" t="n">
-        <v/>
-      </c>
-      <c r="M42" t="n">
-        <v/>
-      </c>
-      <c r="N42" t="n">
-        <v/>
-      </c>
-      <c r="O42" t="n">
-        <v/>
-      </c>
-      <c r="P42" t="n">
-        <v/>
-      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-03; 相对D0=5.85%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3430,24 +2806,12 @@
       <c r="J43" s="4" t="n">
         <v>47.97</v>
       </c>
-      <c r="K43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
+      <c r="P43" s="4" t="n"/>
       <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-03; 相对D0=-0.31%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -3499,24 +2863,12 @@
       <c r="J44" s="4" t="n">
         <v>140.33</v>
       </c>
-      <c r="K44" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M44" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O44" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P44" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="n"/>
+      <c r="O44" s="4" t="n"/>
+      <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="inlineStr">
         <is>
           <t>D0=135.28; 最新=2026-06-03; 相对D0=3.73%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -3568,24 +2920,12 @@
       <c r="J45" s="4" t="n">
         <v>141.5</v>
       </c>
-      <c r="K45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="n"/>
+      <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-03; 相对D0=0.20%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -3637,24 +2977,12 @@
       <c r="J46" s="4" t="n">
         <v>421.21</v>
       </c>
-      <c r="K46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-03; 相对D0=7.63%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -3706,24 +3034,12 @@
       <c r="J47" s="4" t="n">
         <v>959.36</v>
       </c>
-      <c r="K47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="4" t="n"/>
       <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-03; 相对D0=-7.64%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -3775,24 +3091,12 @@
       <c r="J48" s="4" t="n">
         <v>181.67</v>
       </c>
-      <c r="K48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
+      <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-06-03; 相对D0=1.29%; 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
@@ -3844,24 +3148,6 @@
       <c r="J49" t="n">
         <v>368.32</v>
       </c>
-      <c r="K49" t="n">
-        <v/>
-      </c>
-      <c r="L49" t="n">
-        <v/>
-      </c>
-      <c r="M49" t="n">
-        <v/>
-      </c>
-      <c r="N49" t="n">
-        <v/>
-      </c>
-      <c r="O49" t="n">
-        <v/>
-      </c>
-      <c r="P49" t="n">
-        <v/>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-03; 相对D0=12.94%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3913,24 +3199,12 @@
       <c r="J50" s="4" t="n">
         <v>26.37</v>
       </c>
-      <c r="K50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>D0=26.73; 最新=2026-06-03; 相对D0=-1.35%</t>
@@ -3982,24 +3256,12 @@
       <c r="J51" s="4" t="n">
         <v>133.76</v>
       </c>
-      <c r="K51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
+      <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>D0=137.65; 最新=2026-06-03; 相对D0=-2.83%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -4051,24 +3313,6 @@
       <c r="J52" t="n">
         <v>257.73</v>
       </c>
-      <c r="K52" t="n">
-        <v/>
-      </c>
-      <c r="L52" t="n">
-        <v/>
-      </c>
-      <c r="M52" t="n">
-        <v/>
-      </c>
-      <c r="N52" t="n">
-        <v/>
-      </c>
-      <c r="O52" t="n">
-        <v/>
-      </c>
-      <c r="P52" t="n">
-        <v/>
-      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-03; 相对D0=11.09%</t>
@@ -4120,24 +3364,12 @@
       <c r="J53" s="4" t="n">
         <v>279.98</v>
       </c>
-      <c r="K53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n"/>
+      <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-03; 相对D0=6.76%; 历史重复3次; 重复日期=2026-05-26, 2026-05-27, 2026-06-02</t>
@@ -4189,24 +3421,12 @@
       <c r="J54" s="4" t="n">
         <v>59.64</v>
       </c>
-      <c r="K54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="n"/>
+      <c r="P54" s="4" t="n"/>
       <c r="Q54" s="4" t="inlineStr">
         <is>
           <t>D0=58.81; 最新=2026-06-03; 相对D0=1.41%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -4258,24 +3478,6 @@
       <c r="J55" t="n">
         <v>57.29</v>
       </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>D0=54.94; 最新=2026-06-03; 相对D0=4.28%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -4327,24 +3529,6 @@
       <c r="J56" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="K56" t="n">
-        <v/>
-      </c>
-      <c r="L56" t="n">
-        <v/>
-      </c>
-      <c r="M56" t="n">
-        <v/>
-      </c>
-      <c r="N56" t="n">
-        <v/>
-      </c>
-      <c r="O56" t="n">
-        <v/>
-      </c>
-      <c r="P56" t="n">
-        <v/>
-      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>D0=81.76; 最新=2026-06-03; 相对D0=5.92%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -4396,24 +3580,6 @@
       <c r="J57" t="n">
         <v>101.53</v>
       </c>
-      <c r="K57" t="n">
-        <v/>
-      </c>
-      <c r="L57" t="n">
-        <v/>
-      </c>
-      <c r="M57" t="n">
-        <v/>
-      </c>
-      <c r="N57" t="n">
-        <v/>
-      </c>
-      <c r="O57" t="n">
-        <v/>
-      </c>
-      <c r="P57" t="n">
-        <v/>
-      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-03; 相对D0=18.86%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -4465,24 +3631,6 @@
       <c r="J58" t="n">
         <v>423.7</v>
       </c>
-      <c r="K58" t="n">
-        <v/>
-      </c>
-      <c r="L58" t="n">
-        <v/>
-      </c>
-      <c r="M58" t="n">
-        <v/>
-      </c>
-      <c r="N58" t="n">
-        <v/>
-      </c>
-      <c r="O58" t="n">
-        <v/>
-      </c>
-      <c r="P58" t="n">
-        <v/>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-03; 相对D0=-0.54%</t>
@@ -4534,24 +3682,12 @@
       <c r="J59" s="4" t="n">
         <v>14.09</v>
       </c>
-      <c r="K59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="n"/>
+      <c r="N59" s="4" t="n"/>
+      <c r="O59" s="4" t="n"/>
+      <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-03; 相对D0=8.22%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -4603,24 +3739,12 @@
       <c r="J60" s="4" t="n">
         <v>153.8</v>
       </c>
-      <c r="K60" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M60" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O60" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P60" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="n"/>
+      <c r="O60" s="4" t="n"/>
+      <c r="P60" s="4" t="n"/>
       <c r="Q60" s="4" t="inlineStr">
         <is>
           <t>D0=156.27; 最新=2026-06-03; 相对D0=-1.58%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -4672,24 +3796,6 @@
       <c r="J61" t="n">
         <v>51.63</v>
       </c>
-      <c r="K61" t="n">
-        <v/>
-      </c>
-      <c r="L61" t="n">
-        <v/>
-      </c>
-      <c r="M61" t="n">
-        <v/>
-      </c>
-      <c r="N61" t="n">
-        <v/>
-      </c>
-      <c r="O61" t="n">
-        <v/>
-      </c>
-      <c r="P61" t="n">
-        <v/>
-      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>D0=50.29; 最新=2026-06-03; 相对D0=2.66%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -4741,24 +3847,12 @@
       <c r="J62" s="4" t="n">
         <v>75.2</v>
       </c>
-      <c r="K62" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L62" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M62" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N62" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O62" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P62" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n"/>
+      <c r="N62" s="4" t="n"/>
+      <c r="O62" s="4" t="n"/>
+      <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-03; 相对D0=2.37%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -4810,24 +3904,6 @@
       <c r="J63" t="n">
         <v>479.23</v>
       </c>
-      <c r="K63" t="n">
-        <v/>
-      </c>
-      <c r="L63" t="n">
-        <v/>
-      </c>
-      <c r="M63" t="n">
-        <v/>
-      </c>
-      <c r="N63" t="n">
-        <v/>
-      </c>
-      <c r="O63" t="n">
-        <v/>
-      </c>
-      <c r="P63" t="n">
-        <v/>
-      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-03; 相对D0=13.56%</t>
@@ -4879,24 +3955,6 @@
       <c r="J64" t="n">
         <v>90.84999999999999</v>
       </c>
-      <c r="K64" t="n">
-        <v/>
-      </c>
-      <c r="L64" t="n">
-        <v/>
-      </c>
-      <c r="M64" t="n">
-        <v/>
-      </c>
-      <c r="N64" t="n">
-        <v/>
-      </c>
-      <c r="O64" t="n">
-        <v/>
-      </c>
-      <c r="P64" t="n">
-        <v/>
-      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-03; 相对D0=5.04%</t>
@@ -4948,24 +4006,12 @@
       <c r="J65" s="4" t="n">
         <v>184.72</v>
       </c>
-      <c r="K65" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P65" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K65" s="4" t="n"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n"/>
+      <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="n"/>
+      <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="inlineStr">
         <is>
           <t>D0=204.38; 最新=2026-06-03; 相对D0=-9.62%</t>
@@ -5017,24 +4063,12 @@
       <c r="J66" s="4" t="n">
         <v>183.45</v>
       </c>
-      <c r="K66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P66" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="4" t="n"/>
+      <c r="O66" s="4" t="n"/>
+      <c r="P66" s="4" t="n"/>
       <c r="Q66" s="4" t="inlineStr">
         <is>
           <t>D0=174.73; 最新=2026-06-03; 相对D0=4.99%</t>
@@ -5086,24 +4120,12 @@
       <c r="J67" s="4" t="n">
         <v>114.56</v>
       </c>
-      <c r="K67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n"/>
+      <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-03; 相对D0=5.91%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -5155,24 +4177,6 @@
       <c r="J68" t="n">
         <v>110.93</v>
       </c>
-      <c r="K68" t="n">
-        <v/>
-      </c>
-      <c r="L68" t="n">
-        <v/>
-      </c>
-      <c r="M68" t="n">
-        <v/>
-      </c>
-      <c r="N68" t="n">
-        <v/>
-      </c>
-      <c r="O68" t="n">
-        <v/>
-      </c>
-      <c r="P68" t="n">
-        <v/>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-03; 相对D0=4.76%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -5224,24 +4228,12 @@
       <c r="J69" s="4" t="n">
         <v>47.97</v>
       </c>
-      <c r="K69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O69" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P69" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
+      <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="inlineStr">
         <is>
           <t>D0=49.46; 最新=2026-06-03; 相对D0=-3.01%</t>
@@ -5293,24 +4285,12 @@
       <c r="J70" s="4" t="n">
         <v>421.21</v>
       </c>
-      <c r="K70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="4" t="n"/>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="4" t="n"/>
+      <c r="N70" s="4" t="n"/>
+      <c r="O70" s="4" t="n"/>
+      <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="inlineStr">
         <is>
           <t>D0=403.13; 最新=2026-06-03; 相对D0=4.48%</t>
@@ -5362,24 +4342,12 @@
       <c r="J71" s="4" t="n">
         <v>959.36</v>
       </c>
-      <c r="K71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O71" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P71" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K71" s="4" t="n"/>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="4" t="n"/>
+      <c r="N71" s="4" t="n"/>
+      <c r="O71" s="4" t="n"/>
+      <c r="P71" s="4" t="n"/>
       <c r="Q71" s="4" t="inlineStr">
         <is>
           <t>D0=1070.47; 最新=2026-06-03; 相对D0=-10.38%</t>
@@ -5431,24 +4399,6 @@
       <c r="J72" t="n">
         <v>358.99</v>
       </c>
-      <c r="K72" t="n">
-        <v/>
-      </c>
-      <c r="L72" t="n">
-        <v/>
-      </c>
-      <c r="M72" t="n">
-        <v/>
-      </c>
-      <c r="N72" t="n">
-        <v/>
-      </c>
-      <c r="O72" t="n">
-        <v/>
-      </c>
-      <c r="P72" t="n">
-        <v/>
-      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-03; 相对D0=-7.69%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -5500,24 +4450,12 @@
       <c r="J73" s="4" t="n">
         <v>181.67</v>
       </c>
-      <c r="K73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O73" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P73" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n"/>
+      <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="inlineStr">
         <is>
           <t>D0=183.36; 最新=2026-06-03; 相对D0=-0.92%</t>
@@ -5569,24 +4507,6 @@
       <c r="J74" t="n">
         <v>68.42</v>
       </c>
-      <c r="K74" t="n">
-        <v/>
-      </c>
-      <c r="L74" t="n">
-        <v/>
-      </c>
-      <c r="M74" t="n">
-        <v/>
-      </c>
-      <c r="N74" t="n">
-        <v/>
-      </c>
-      <c r="O74" t="n">
-        <v/>
-      </c>
-      <c r="P74" t="n">
-        <v/>
-      </c>
       <c r="Q74" t="inlineStr">
         <is>
           <t>D0=69.63; 最新=2026-06-03; 相对D0=-1.74%</t>
@@ -5638,24 +4558,6 @@
       <c r="J75" t="n">
         <v>622.98</v>
       </c>
-      <c r="K75" t="n">
-        <v/>
-      </c>
-      <c r="L75" t="n">
-        <v/>
-      </c>
-      <c r="M75" t="n">
-        <v/>
-      </c>
-      <c r="N75" t="n">
-        <v/>
-      </c>
-      <c r="O75" t="n">
-        <v/>
-      </c>
-      <c r="P75" t="n">
-        <v/>
-      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-03; 相对D0=1.74%</t>
@@ -5707,24 +4609,6 @@
       <c r="J76" t="n">
         <v>23.3</v>
       </c>
-      <c r="K76" t="n">
-        <v/>
-      </c>
-      <c r="L76" t="n">
-        <v/>
-      </c>
-      <c r="M76" t="n">
-        <v/>
-      </c>
-      <c r="N76" t="n">
-        <v/>
-      </c>
-      <c r="O76" t="n">
-        <v/>
-      </c>
-      <c r="P76" t="n">
-        <v/>
-      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>D0=22.62; 最新=2026-06-03; 相对D0=3.01%</t>
@@ -5776,24 +4660,12 @@
       <c r="J77" s="4" t="n">
         <v>131.83</v>
       </c>
-      <c r="K77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O77" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P77" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K77" s="4" t="n"/>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="4" t="n"/>
+      <c r="N77" s="4" t="n"/>
+      <c r="O77" s="4" t="n"/>
+      <c r="P77" s="4" t="n"/>
       <c r="Q77" s="4" t="inlineStr">
         <is>
           <t>D0=134.61; 最新=2026-06-03; 相对D0=-2.07%; 历史重复2次; 重复日期=2026-05-28, 2026-06-02</t>
@@ -5845,24 +4717,12 @@
       <c r="J78" s="4" t="n">
         <v>65.20999999999999</v>
       </c>
-      <c r="K78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P78" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K78" s="4" t="n"/>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="4" t="n"/>
+      <c r="N78" s="4" t="n"/>
+      <c r="O78" s="4" t="n"/>
+      <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-03; 相对D0=-5.08%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -5914,24 +4774,12 @@
       <c r="J79" s="4" t="n">
         <v>279.98</v>
       </c>
-      <c r="K79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P79" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K79" s="4" t="n"/>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="4" t="n"/>
+      <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="inlineStr">
         <is>
           <t>D0=274.17; 最新=2026-06-03; 相对D0=2.12%</t>
@@ -5983,24 +4831,6 @@
       <c r="J80" t="n">
         <v>57.29</v>
       </c>
-      <c r="K80" t="n">
-        <v/>
-      </c>
-      <c r="L80" t="n">
-        <v/>
-      </c>
-      <c r="M80" t="n">
-        <v/>
-      </c>
-      <c r="N80" t="n">
-        <v/>
-      </c>
-      <c r="O80" t="n">
-        <v/>
-      </c>
-      <c r="P80" t="n">
-        <v/>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>D0=56.31; 最新=2026-06-03; 相对D0=1.74%</t>
@@ -6052,24 +4882,6 @@
       <c r="J81" t="n">
         <v>107.86</v>
       </c>
-      <c r="K81" t="n">
-        <v/>
-      </c>
-      <c r="L81" t="n">
-        <v/>
-      </c>
-      <c r="M81" t="n">
-        <v/>
-      </c>
-      <c r="N81" t="n">
-        <v/>
-      </c>
-      <c r="O81" t="n">
-        <v/>
-      </c>
-      <c r="P81" t="n">
-        <v/>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-03; 相对D0=0.86%</t>
@@ -6121,24 +4933,12 @@
       <c r="J82" s="4" t="n">
         <v>12.27</v>
       </c>
-      <c r="K82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P82" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K82" s="4" t="n"/>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
+      <c r="N82" s="4" t="n"/>
+      <c r="O82" s="4" t="n"/>
+      <c r="P82" s="4" t="n"/>
       <c r="Q82" s="4" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-03; 相对D0=0.41%</t>
@@ -6190,24 +4990,6 @@
       <c r="J83" t="n">
         <v>16.68</v>
       </c>
-      <c r="K83" t="n">
-        <v/>
-      </c>
-      <c r="L83" t="n">
-        <v/>
-      </c>
-      <c r="M83" t="n">
-        <v/>
-      </c>
-      <c r="N83" t="n">
-        <v/>
-      </c>
-      <c r="O83" t="n">
-        <v/>
-      </c>
-      <c r="P83" t="n">
-        <v/>
-      </c>
       <c r="Q83" t="inlineStr">
         <is>
           <t>D0=15.98; 最新=2026-06-03; 相对D0=4.38%</t>
@@ -6259,24 +5041,6 @@
       <c r="J84" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="K84" t="n">
-        <v/>
-      </c>
-      <c r="L84" t="n">
-        <v/>
-      </c>
-      <c r="M84" t="n">
-        <v/>
-      </c>
-      <c r="N84" t="n">
-        <v/>
-      </c>
-      <c r="O84" t="n">
-        <v/>
-      </c>
-      <c r="P84" t="n">
-        <v/>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-03; 相对D0=2.32%</t>
@@ -6328,24 +5092,12 @@
       <c r="J85" s="4" t="n">
         <v>14.09</v>
       </c>
-      <c r="K85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P85" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="4" t="n"/>
+      <c r="O85" s="4" t="n"/>
+      <c r="P85" s="4" t="n"/>
       <c r="Q85" s="4" t="inlineStr">
         <is>
           <t>D0=13.51; 最新=2026-06-03; 相对D0=4.29%</t>
@@ -6397,24 +5149,12 @@
       <c r="J86" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="K86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="4" t="n"/>
+      <c r="L86" s="4" t="n"/>
+      <c r="M86" s="4" t="n"/>
+      <c r="N86" s="4" t="n"/>
+      <c r="O86" s="4" t="n"/>
+      <c r="P86" s="4" t="n"/>
       <c r="Q86" s="4" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-06-03; 相对D0=-2.17%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -6466,24 +5206,6 @@
       <c r="J87" t="n">
         <v>331.44</v>
       </c>
-      <c r="K87" t="n">
-        <v/>
-      </c>
-      <c r="L87" t="n">
-        <v/>
-      </c>
-      <c r="M87" t="n">
-        <v/>
-      </c>
-      <c r="N87" t="n">
-        <v/>
-      </c>
-      <c r="O87" t="n">
-        <v/>
-      </c>
-      <c r="P87" t="n">
-        <v/>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-03; 相对D0=2.32%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -6535,24 +5257,6 @@
       <c r="J88" t="n">
         <v>51.63</v>
       </c>
-      <c r="K88" t="n">
-        <v/>
-      </c>
-      <c r="L88" t="n">
-        <v/>
-      </c>
-      <c r="M88" t="n">
-        <v/>
-      </c>
-      <c r="N88" t="n">
-        <v/>
-      </c>
-      <c r="O88" t="n">
-        <v/>
-      </c>
-      <c r="P88" t="n">
-        <v/>
-      </c>
       <c r="Q88" t="inlineStr">
         <is>
           <t>D0=50.99; 最新=2026-06-03; 相对D0=1.26%</t>
@@ -6604,24 +5308,12 @@
       <c r="J89" s="4" t="n">
         <v>184.07</v>
       </c>
-      <c r="K89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="4" t="n"/>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
+      <c r="N89" s="4" t="n"/>
+      <c r="O89" s="4" t="n"/>
+      <c r="P89" s="4" t="n"/>
       <c r="Q89" s="4" t="inlineStr">
         <is>
           <t>D0=179.83; 最新=2026-06-03; 相对D0=2.36%</t>
@@ -6673,24 +5365,6 @@
       <c r="J90" t="n">
         <v>250.02</v>
       </c>
-      <c r="K90" t="n">
-        <v/>
-      </c>
-      <c r="L90" t="n">
-        <v/>
-      </c>
-      <c r="M90" t="n">
-        <v/>
-      </c>
-      <c r="N90" t="n">
-        <v/>
-      </c>
-      <c r="O90" t="n">
-        <v/>
-      </c>
-      <c r="P90" t="n">
-        <v/>
-      </c>
       <c r="Q90" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-03; 相对D0=-8.03%</t>
@@ -6711,7 +5385,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6738,24 +5411,6 @@
       <c r="J91" t="n">
         <v>88.62</v>
       </c>
-      <c r="K91" t="n">
-        <v/>
-      </c>
-      <c r="L91" t="n">
-        <v/>
-      </c>
-      <c r="M91" t="n">
-        <v/>
-      </c>
-      <c r="N91" t="n">
-        <v/>
-      </c>
-      <c r="O91" t="n">
-        <v/>
-      </c>
-      <c r="P91" t="n">
-        <v/>
-      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-03; 相对D0=-2.48%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -6807,24 +5462,6 @@
       <c r="J92" t="n">
         <v>16.42</v>
       </c>
-      <c r="K92" t="n">
-        <v/>
-      </c>
-      <c r="L92" t="n">
-        <v/>
-      </c>
-      <c r="M92" t="n">
-        <v/>
-      </c>
-      <c r="N92" t="n">
-        <v/>
-      </c>
-      <c r="O92" t="n">
-        <v/>
-      </c>
-      <c r="P92" t="n">
-        <v/>
-      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>D0=16.46; 最新=2026-06-03; 相对D0=-0.24%</t>
@@ -6876,24 +5513,6 @@
       <c r="J93" t="n">
         <v>27.51</v>
       </c>
-      <c r="K93" t="n">
-        <v/>
-      </c>
-      <c r="L93" t="n">
-        <v/>
-      </c>
-      <c r="M93" t="n">
-        <v/>
-      </c>
-      <c r="N93" t="n">
-        <v/>
-      </c>
-      <c r="O93" t="n">
-        <v/>
-      </c>
-      <c r="P93" t="n">
-        <v/>
-      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>D0=25.20; 最新=2026-06-03; 相对D0=9.17%</t>
@@ -6945,24 +5564,6 @@
       <c r="J94" t="n">
         <v>82.84999999999999</v>
       </c>
-      <c r="K94" t="n">
-        <v/>
-      </c>
-      <c r="L94" t="n">
-        <v/>
-      </c>
-      <c r="M94" t="n">
-        <v/>
-      </c>
-      <c r="N94" t="n">
-        <v/>
-      </c>
-      <c r="O94" t="n">
-        <v/>
-      </c>
-      <c r="P94" t="n">
-        <v/>
-      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>D0=76.23; 最新=2026-06-03; 相对D0=8.68%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -7014,24 +5615,6 @@
       <c r="J95" t="n">
         <v>50.01</v>
       </c>
-      <c r="K95" t="n">
-        <v/>
-      </c>
-      <c r="L95" t="n">
-        <v/>
-      </c>
-      <c r="M95" t="n">
-        <v/>
-      </c>
-      <c r="N95" t="n">
-        <v/>
-      </c>
-      <c r="O95" t="n">
-        <v/>
-      </c>
-      <c r="P95" t="n">
-        <v/>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>D0=50.44; 最新=2026-06-03; 相对D0=-0.85%</t>
@@ -7083,24 +5666,6 @@
       <c r="J96" t="n">
         <v>117.9</v>
       </c>
-      <c r="K96" t="n">
-        <v/>
-      </c>
-      <c r="L96" t="n">
-        <v/>
-      </c>
-      <c r="M96" t="n">
-        <v/>
-      </c>
-      <c r="N96" t="n">
-        <v/>
-      </c>
-      <c r="O96" t="n">
-        <v/>
-      </c>
-      <c r="P96" t="n">
-        <v/>
-      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-03; 相对D0=15.45%</t>
@@ -7152,24 +5717,12 @@
       <c r="J97" s="4" t="n">
         <v>279.98</v>
       </c>
-      <c r="K97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P97" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K97" s="4" t="n"/>
+      <c r="L97" s="4" t="n"/>
+      <c r="M97" s="4" t="n"/>
+      <c r="N97" s="4" t="n"/>
+      <c r="O97" s="4" t="n"/>
+      <c r="P97" s="4" t="n"/>
       <c r="Q97" s="4" t="inlineStr">
         <is>
           <t>D0=266.89; 最新=2026-06-03; 相对D0=4.90%</t>
@@ -7221,24 +5774,6 @@
       <c r="J98" t="n">
         <v>230.33</v>
       </c>
-      <c r="K98" t="n">
-        <v/>
-      </c>
-      <c r="L98" t="n">
-        <v/>
-      </c>
-      <c r="M98" t="n">
-        <v/>
-      </c>
-      <c r="N98" t="n">
-        <v/>
-      </c>
-      <c r="O98" t="n">
-        <v/>
-      </c>
-      <c r="P98" t="n">
-        <v/>
-      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-03; 相对D0=20.62%</t>
@@ -7290,24 +5825,6 @@
       <c r="J99" t="n">
         <v>101.53</v>
       </c>
-      <c r="K99" t="n">
-        <v/>
-      </c>
-      <c r="L99" t="n">
-        <v/>
-      </c>
-      <c r="M99" t="n">
-        <v/>
-      </c>
-      <c r="N99" t="n">
-        <v/>
-      </c>
-      <c r="O99" t="n">
-        <v/>
-      </c>
-      <c r="P99" t="n">
-        <v/>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>D0=89.07; 最新=2026-06-03; 相对D0=13.99%</t>
@@ -7359,24 +5876,6 @@
       <c r="J100" t="n">
         <v>377</v>
       </c>
-      <c r="K100" t="n">
-        <v/>
-      </c>
-      <c r="L100" t="n">
-        <v/>
-      </c>
-      <c r="M100" t="n">
-        <v/>
-      </c>
-      <c r="N100" t="n">
-        <v/>
-      </c>
-      <c r="O100" t="n">
-        <v/>
-      </c>
-      <c r="P100" t="n">
-        <v/>
-      </c>
       <c r="Q100" t="inlineStr">
         <is>
           <t>D0=384.01; 最新=2026-06-03; 相对D0=-1.83%</t>
@@ -7428,24 +5927,6 @@
       <c r="J101" t="n">
         <v>287.32</v>
       </c>
-      <c r="K101" t="n">
-        <v/>
-      </c>
-      <c r="L101" t="n">
-        <v/>
-      </c>
-      <c r="M101" t="n">
-        <v/>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
-      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-03; 相对D0=-0.93%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -7466,7 +5947,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7493,24 +5973,6 @@
       <c r="J102" t="n">
         <v>88.62</v>
       </c>
-      <c r="K102" t="n">
-        <v/>
-      </c>
-      <c r="L102" t="n">
-        <v/>
-      </c>
-      <c r="M102" t="n">
-        <v/>
-      </c>
-      <c r="N102" t="n">
-        <v/>
-      </c>
-      <c r="O102" t="n">
-        <v/>
-      </c>
-      <c r="P102" t="n">
-        <v/>
-      </c>
       <c r="Q102" t="inlineStr">
         <is>
           <t>D0=91.09; 最新=2026-06-03; 相对D0=-2.71%</t>
@@ -7562,24 +6024,12 @@
       <c r="J103" s="4" t="n">
         <v>114.56</v>
       </c>
-      <c r="K103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P103" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="4" t="n"/>
+      <c r="O103" s="4" t="n"/>
+      <c r="P103" s="4" t="n"/>
       <c r="Q103" s="4" t="inlineStr">
         <is>
           <t>D0=110.63; 最新=2026-06-03; 相对D0=3.55%</t>
@@ -7631,24 +6081,6 @@
       <c r="J104" t="n">
         <v>91.67</v>
       </c>
-      <c r="K104" t="n">
-        <v/>
-      </c>
-      <c r="L104" t="n">
-        <v/>
-      </c>
-      <c r="M104" t="n">
-        <v/>
-      </c>
-      <c r="N104" t="n">
-        <v/>
-      </c>
-      <c r="O104" t="n">
-        <v/>
-      </c>
-      <c r="P104" t="n">
-        <v/>
-      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>D0=83.68; 最新=2026-06-03; 相对D0=9.55%</t>
@@ -7700,24 +6132,6 @@
       <c r="J105" t="n">
         <v>190.61</v>
       </c>
-      <c r="K105" t="n">
-        <v/>
-      </c>
-      <c r="L105" t="n">
-        <v/>
-      </c>
-      <c r="M105" t="n">
-        <v/>
-      </c>
-      <c r="N105" t="n">
-        <v/>
-      </c>
-      <c r="O105" t="n">
-        <v/>
-      </c>
-      <c r="P105" t="n">
-        <v/>
-      </c>
       <c r="Q105" t="inlineStr">
         <is>
           <t>D0=176.17; 最新=2026-06-03; 相对D0=8.20%</t>
@@ -7769,24 +6183,6 @@
       <c r="J106" t="n">
         <v>747.61</v>
       </c>
-      <c r="K106" t="n">
-        <v/>
-      </c>
-      <c r="L106" t="n">
-        <v/>
-      </c>
-      <c r="M106" t="n">
-        <v/>
-      </c>
-      <c r="N106" t="n">
-        <v/>
-      </c>
-      <c r="O106" t="n">
-        <v/>
-      </c>
-      <c r="P106" t="n">
-        <v/>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-03; 相对D0=11.42%</t>
@@ -7838,24 +6234,6 @@
       <c r="J107" t="n">
         <v>110.93</v>
       </c>
-      <c r="K107" t="n">
-        <v/>
-      </c>
-      <c r="L107" t="n">
-        <v/>
-      </c>
-      <c r="M107" t="n">
-        <v/>
-      </c>
-      <c r="N107" t="n">
-        <v/>
-      </c>
-      <c r="O107" t="n">
-        <v/>
-      </c>
-      <c r="P107" t="n">
-        <v/>
-      </c>
       <c r="Q107" t="inlineStr">
         <is>
           <t>D0=106.86; 最新=2026-06-03; 相对D0=3.81%</t>
@@ -7907,24 +6285,6 @@
       <c r="J108" t="n">
         <v>65.45999999999999</v>
       </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
-      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-03; 相对D0=-2.85%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -7945,7 +6305,6 @@
           <t>EQIX</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7972,24 +6331,6 @@
       <c r="J109" t="n">
         <v>1077</v>
       </c>
-      <c r="K109" t="n">
-        <v/>
-      </c>
-      <c r="L109" t="n">
-        <v/>
-      </c>
-      <c r="M109" t="n">
-        <v/>
-      </c>
-      <c r="N109" t="n">
-        <v/>
-      </c>
-      <c r="O109" t="n">
-        <v/>
-      </c>
-      <c r="P109" t="n">
-        <v/>
-      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-03; 相对D0=0.71%</t>
@@ -8041,24 +6382,6 @@
       <c r="J110" t="n">
         <v>146.48</v>
       </c>
-      <c r="K110" t="n">
-        <v/>
-      </c>
-      <c r="L110" t="n">
-        <v/>
-      </c>
-      <c r="M110" t="n">
-        <v/>
-      </c>
-      <c r="N110" t="n">
-        <v/>
-      </c>
-      <c r="O110" t="n">
-        <v/>
-      </c>
-      <c r="P110" t="n">
-        <v/>
-      </c>
       <c r="Q110" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-03; 相对D0=12.94%</t>
@@ -8110,24 +6433,6 @@
       <c r="J111" t="n">
         <v>358.99</v>
       </c>
-      <c r="K111" t="n">
-        <v/>
-      </c>
-      <c r="L111" t="n">
-        <v/>
-      </c>
-      <c r="M111" t="n">
-        <v/>
-      </c>
-      <c r="N111" t="n">
-        <v/>
-      </c>
-      <c r="O111" t="n">
-        <v/>
-      </c>
-      <c r="P111" t="n">
-        <v/>
-      </c>
       <c r="Q111" t="inlineStr">
         <is>
           <t>D0=390.13; 最新=2026-06-03; 相对D0=-7.98%</t>
@@ -8179,24 +6484,6 @@
       <c r="J112" t="n">
         <v>82.84999999999999</v>
       </c>
-      <c r="K112" t="n">
-        <v/>
-      </c>
-      <c r="L112" t="n">
-        <v/>
-      </c>
-      <c r="M112" t="n">
-        <v/>
-      </c>
-      <c r="N112" t="n">
-        <v/>
-      </c>
-      <c r="O112" t="n">
-        <v/>
-      </c>
-      <c r="P112" t="n">
-        <v/>
-      </c>
       <c r="Q112" t="inlineStr">
         <is>
           <t>D0=84.84; 最新=2026-06-03; 相对D0=-2.35%</t>
@@ -8248,24 +6535,6 @@
       <c r="J113" t="n">
         <v>100.2</v>
       </c>
-      <c r="K113" t="n">
-        <v/>
-      </c>
-      <c r="L113" t="n">
-        <v/>
-      </c>
-      <c r="M113" t="n">
-        <v/>
-      </c>
-      <c r="N113" t="n">
-        <v/>
-      </c>
-      <c r="O113" t="n">
-        <v/>
-      </c>
-      <c r="P113" t="n">
-        <v/>
-      </c>
       <c r="Q113" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-03; 相对D0=4.72%</t>
@@ -8317,24 +6586,12 @@
       <c r="J114" s="4" t="n">
         <v>181.67</v>
       </c>
-      <c r="K114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P114" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K114" s="4" t="n"/>
+      <c r="L114" s="4" t="n"/>
+      <c r="M114" s="4" t="n"/>
+      <c r="N114" s="4" t="n"/>
+      <c r="O114" s="4" t="n"/>
+      <c r="P114" s="4" t="n"/>
       <c r="Q114" s="4" t="inlineStr">
         <is>
           <t>D0=185.46; 最新=2026-06-03; 相对D0=-2.04%</t>
@@ -8386,24 +6643,6 @@
       <c r="J115" t="n">
         <v>368.32</v>
       </c>
-      <c r="K115" t="n">
-        <v/>
-      </c>
-      <c r="L115" t="n">
-        <v/>
-      </c>
-      <c r="M115" t="n">
-        <v/>
-      </c>
-      <c r="N115" t="n">
-        <v/>
-      </c>
-      <c r="O115" t="n">
-        <v/>
-      </c>
-      <c r="P115" t="n">
-        <v/>
-      </c>
       <c r="Q115" t="inlineStr">
         <is>
           <t>D0=325.68; 最新=2026-06-03; 相对D0=13.09%</t>
@@ -8455,24 +6694,6 @@
       <c r="J116" t="n">
         <v>427.34</v>
       </c>
-      <c r="K116" t="n">
-        <v/>
-      </c>
-      <c r="L116" t="n">
-        <v/>
-      </c>
-      <c r="M116" t="n">
-        <v/>
-      </c>
-      <c r="N116" t="n">
-        <v/>
-      </c>
-      <c r="O116" t="n">
-        <v/>
-      </c>
-      <c r="P116" t="n">
-        <v/>
-      </c>
       <c r="Q116" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-03; 相对D0=0.08%</t>
@@ -8524,24 +6745,6 @@
       <c r="J117" t="n">
         <v>251.68</v>
       </c>
-      <c r="K117" t="n">
-        <v/>
-      </c>
-      <c r="L117" t="n">
-        <v/>
-      </c>
-      <c r="M117" t="n">
-        <v/>
-      </c>
-      <c r="N117" t="n">
-        <v/>
-      </c>
-      <c r="O117" t="n">
-        <v/>
-      </c>
-      <c r="P117" t="n">
-        <v/>
-      </c>
       <c r="Q117" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-03; 相对D0=11.20%</t>
@@ -8593,24 +6796,12 @@
       <c r="J118" s="4" t="n">
         <v>131.83</v>
       </c>
-      <c r="K118" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L118" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M118" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N118" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O118" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P118" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K118" s="4" t="n"/>
+      <c r="L118" s="4" t="n"/>
+      <c r="M118" s="4" t="n"/>
+      <c r="N118" s="4" t="n"/>
+      <c r="O118" s="4" t="n"/>
+      <c r="P118" s="4" t="n"/>
       <c r="Q118" s="4" t="inlineStr">
         <is>
           <t>D0=133.31; 最新=2026-06-03; 相对D0=-1.11%</t>
@@ -8662,24 +6853,6 @@
       <c r="J119" t="n">
         <v>124.65</v>
       </c>
-      <c r="K119" t="n">
-        <v/>
-      </c>
-      <c r="L119" t="n">
-        <v/>
-      </c>
-      <c r="M119" t="n">
-        <v/>
-      </c>
-      <c r="N119" t="n">
-        <v/>
-      </c>
-      <c r="O119" t="n">
-        <v/>
-      </c>
-      <c r="P119" t="n">
-        <v/>
-      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-03; 相对D0=31.60%</t>
@@ -8731,24 +6904,6 @@
       <c r="J120" t="n">
         <v>280.43</v>
       </c>
-      <c r="K120" t="n">
-        <v/>
-      </c>
-      <c r="L120" t="n">
-        <v/>
-      </c>
-      <c r="M120" t="n">
-        <v/>
-      </c>
-      <c r="N120" t="n">
-        <v/>
-      </c>
-      <c r="O120" t="n">
-        <v/>
-      </c>
-      <c r="P120" t="n">
-        <v/>
-      </c>
       <c r="Q120" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-03; 相对D0=8.79%</t>
@@ -8800,24 +6955,6 @@
       <c r="J121" t="n">
         <v>142.2</v>
       </c>
-      <c r="K121" t="n">
-        <v/>
-      </c>
-      <c r="L121" t="n">
-        <v/>
-      </c>
-      <c r="M121" t="n">
-        <v/>
-      </c>
-      <c r="N121" t="n">
-        <v/>
-      </c>
-      <c r="O121" t="n">
-        <v/>
-      </c>
-      <c r="P121" t="n">
-        <v/>
-      </c>
       <c r="Q121" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-03; 相对D0=-0.80%</t>
@@ -8869,24 +7006,6 @@
       <c r="J122" t="n">
         <v>256.24</v>
       </c>
-      <c r="K122" t="n">
-        <v/>
-      </c>
-      <c r="L122" t="n">
-        <v/>
-      </c>
-      <c r="M122" t="n">
-        <v/>
-      </c>
-      <c r="N122" t="n">
-        <v/>
-      </c>
-      <c r="O122" t="n">
-        <v/>
-      </c>
-      <c r="P122" t="n">
-        <v/>
-      </c>
       <c r="Q122" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-03; 相对D0=-1.15%</t>
@@ -8938,24 +7057,12 @@
       <c r="J123" s="4" t="n">
         <v>183.45</v>
       </c>
-      <c r="K123" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L123" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M123" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N123" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O123" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P123" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K123" s="4" t="n"/>
+      <c r="L123" s="4" t="n"/>
+      <c r="M123" s="4" t="n"/>
+      <c r="N123" s="4" t="n"/>
+      <c r="O123" s="4" t="n"/>
+      <c r="P123" s="4" t="n"/>
       <c r="Q123" s="4" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-03; 相对D0=6.87%</t>
@@ -9007,24 +7114,12 @@
       <c r="J124" s="4" t="n">
         <v>267.24</v>
       </c>
-      <c r="K124" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L124" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M124" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N124" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O124" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P124" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K124" s="4" t="n"/>
+      <c r="L124" s="4" t="n"/>
+      <c r="M124" s="4" t="n"/>
+      <c r="N124" s="4" t="n"/>
+      <c r="O124" s="4" t="n"/>
+      <c r="P124" s="4" t="n"/>
       <c r="Q124" s="4" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-03; 相对D0=-7.13%</t>
@@ -9076,24 +7171,6 @@
       <c r="J125" t="n">
         <v>163.22</v>
       </c>
-      <c r="K125" t="n">
-        <v/>
-      </c>
-      <c r="L125" t="n">
-        <v/>
-      </c>
-      <c r="M125" t="n">
-        <v/>
-      </c>
-      <c r="N125" t="n">
-        <v/>
-      </c>
-      <c r="O125" t="n">
-        <v/>
-      </c>
-      <c r="P125" t="n">
-        <v/>
-      </c>
       <c r="Q125" t="inlineStr">
         <is>
           <t>D0=189.03; 最新=2026-06-03; 相对D0=-13.65%</t>
@@ -9145,24 +7222,6 @@
       <c r="J126" t="n">
         <v>190.61</v>
       </c>
-      <c r="K126" t="n">
-        <v/>
-      </c>
-      <c r="L126" t="n">
-        <v/>
-      </c>
-      <c r="M126" t="n">
-        <v/>
-      </c>
-      <c r="N126" t="n">
-        <v/>
-      </c>
-      <c r="O126" t="n">
-        <v/>
-      </c>
-      <c r="P126" t="n">
-        <v/>
-      </c>
       <c r="Q126" t="inlineStr">
         <is>
           <t>D0=191.10; 最新=2026-06-03; 相对D0=-0.26%</t>
@@ -9214,24 +7273,6 @@
       <c r="J127" t="n">
         <v>110.93</v>
       </c>
-      <c r="K127" t="n">
-        <v/>
-      </c>
-      <c r="L127" t="n">
-        <v/>
-      </c>
-      <c r="M127" t="n">
-        <v/>
-      </c>
-      <c r="N127" t="n">
-        <v/>
-      </c>
-      <c r="O127" t="n">
-        <v/>
-      </c>
-      <c r="P127" t="n">
-        <v/>
-      </c>
       <c r="Q127" t="inlineStr">
         <is>
           <t>D0=109.53; 最新=2026-06-03; 相对D0=1.28%</t>
@@ -9283,24 +7324,12 @@
       <c r="J128" s="4" t="n">
         <v>47.97</v>
       </c>
-      <c r="K128" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L128" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M128" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N128" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O128" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P128" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K128" s="4" t="n"/>
+      <c r="L128" s="4" t="n"/>
+      <c r="M128" s="4" t="n"/>
+      <c r="N128" s="4" t="n"/>
+      <c r="O128" s="4" t="n"/>
+      <c r="P128" s="4" t="n"/>
       <c r="Q128" s="4" t="inlineStr">
         <is>
           <t>D0=48.42; 最新=2026-06-03; 相对D0=-0.93%</t>
@@ -9352,24 +7381,6 @@
       <c r="J129" t="n">
         <v>2125.1101</v>
       </c>
-      <c r="K129" t="n">
-        <v/>
-      </c>
-      <c r="L129" t="n">
-        <v/>
-      </c>
-      <c r="M129" t="n">
-        <v/>
-      </c>
-      <c r="N129" t="n">
-        <v/>
-      </c>
-      <c r="O129" t="n">
-        <v/>
-      </c>
-      <c r="P129" t="n">
-        <v/>
-      </c>
       <c r="Q129" t="inlineStr">
         <is>
           <t>D0=1921.71; 最新=2026-06-03; 相对D0=10.58%</t>
@@ -9421,24 +7432,6 @@
       <c r="J130" t="n">
         <v>368.32</v>
       </c>
-      <c r="K130" t="n">
-        <v/>
-      </c>
-      <c r="L130" t="n">
-        <v/>
-      </c>
-      <c r="M130" t="n">
-        <v/>
-      </c>
-      <c r="N130" t="n">
-        <v/>
-      </c>
-      <c r="O130" t="n">
-        <v/>
-      </c>
-      <c r="P130" t="n">
-        <v/>
-      </c>
       <c r="Q130" t="inlineStr">
         <is>
           <t>D0=335.55; 最新=2026-06-03; 相对D0=9.77%</t>
@@ -9490,24 +7483,6 @@
       <c r="J131" t="n">
         <v>214.75</v>
       </c>
-      <c r="K131" t="n">
-        <v/>
-      </c>
-      <c r="L131" t="n">
-        <v/>
-      </c>
-      <c r="M131" t="n">
-        <v/>
-      </c>
-      <c r="N131" t="n">
-        <v/>
-      </c>
-      <c r="O131" t="n">
-        <v/>
-      </c>
-      <c r="P131" t="n">
-        <v/>
-      </c>
       <c r="Q131" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-03; 相对D0=1.71%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -9559,24 +7534,12 @@
       <c r="J132" s="4" t="n">
         <v>409.67</v>
       </c>
-      <c r="K132" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L132" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M132" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N132" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O132" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P132" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K132" s="4" t="n"/>
+      <c r="L132" s="4" t="n"/>
+      <c r="M132" s="4" t="n"/>
+      <c r="N132" s="4" t="n"/>
+      <c r="O132" s="4" t="n"/>
+      <c r="P132" s="4" t="n"/>
       <c r="Q132" s="4" t="inlineStr">
         <is>
           <t>D0=374.31; 最新=2026-06-03; 相对D0=9.45%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -9628,24 +7591,12 @@
       <c r="J133" s="4" t="n">
         <v>14.09</v>
       </c>
-      <c r="K133" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L133" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M133" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N133" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O133" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P133" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K133" s="4" t="n"/>
+      <c r="L133" s="4" t="n"/>
+      <c r="M133" s="4" t="n"/>
+      <c r="N133" s="4" t="n"/>
+      <c r="O133" s="4" t="n"/>
+      <c r="P133" s="4" t="n"/>
       <c r="Q133" s="4" t="inlineStr">
         <is>
           <t>D0=13.77; 最新=2026-06-03; 相对D0=2.32%</t>
@@ -9697,24 +7648,6 @@
       <c r="J134" t="n">
         <v>50.87</v>
       </c>
-      <c r="K134" t="n">
-        <v/>
-      </c>
-      <c r="L134" t="n">
-        <v/>
-      </c>
-      <c r="M134" t="n">
-        <v/>
-      </c>
-      <c r="N134" t="n">
-        <v/>
-      </c>
-      <c r="O134" t="n">
-        <v/>
-      </c>
-      <c r="P134" t="n">
-        <v/>
-      </c>
       <c r="Q134" t="inlineStr">
         <is>
           <t>D0=51.58; 最新=2026-06-03; 相对D0=-1.38%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -9766,24 +7699,12 @@
       <c r="J135" s="4" t="n">
         <v>184.07</v>
       </c>
-      <c r="K135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P135" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K135" s="4" t="n"/>
+      <c r="L135" s="4" t="n"/>
+      <c r="M135" s="4" t="n"/>
+      <c r="N135" s="4" t="n"/>
+      <c r="O135" s="4" t="n"/>
+      <c r="P135" s="4" t="n"/>
       <c r="Q135" s="4" t="inlineStr">
         <is>
           <t>D0=185.67; 最新=2026-06-03; 相对D0=-0.86%</t>
@@ -9835,24 +7756,12 @@
       <c r="J136" s="4" t="n">
         <v>14.71</v>
       </c>
-      <c r="K136" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L136" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M136" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N136" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O136" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P136" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K136" s="4" t="n"/>
+      <c r="L136" s="4" t="n"/>
+      <c r="M136" s="4" t="n"/>
+      <c r="N136" s="4" t="n"/>
+      <c r="O136" s="4" t="n"/>
+      <c r="P136" s="4" t="n"/>
       <c r="Q136" s="4" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-03; 相对D0=0.07%</t>
@@ -9904,24 +7813,12 @@
       <c r="J137" s="4" t="n">
         <v>75.2</v>
       </c>
-      <c r="K137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P137" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K137" s="4" t="n"/>
+      <c r="L137" s="4" t="n"/>
+      <c r="M137" s="4" t="n"/>
+      <c r="N137" s="4" t="n"/>
+      <c r="O137" s="4" t="n"/>
+      <c r="P137" s="4" t="n"/>
       <c r="Q137" s="4" t="inlineStr">
         <is>
           <t>D0=72.75; 最新=2026-06-03; 相对D0=3.37%</t>
@@ -9973,24 +7870,6 @@
       <c r="J138" t="n">
         <v>315.6</v>
       </c>
-      <c r="K138" t="n">
-        <v/>
-      </c>
-      <c r="L138" t="n">
-        <v/>
-      </c>
-      <c r="M138" t="n">
-        <v/>
-      </c>
-      <c r="N138" t="n">
-        <v/>
-      </c>
-      <c r="O138" t="n">
-        <v/>
-      </c>
-      <c r="P138" t="n">
-        <v/>
-      </c>
       <c r="Q138" t="inlineStr">
         <is>
           <t>D0=320.41; 最新=2026-06-03; 相对D0=-1.50%</t>
@@ -10042,24 +7921,12 @@
       <c r="J139" s="4" t="n">
         <v>189.71</v>
       </c>
-      <c r="K139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P139" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K139" s="4" t="n"/>
+      <c r="L139" s="4" t="n"/>
+      <c r="M139" s="4" t="n"/>
+      <c r="N139" s="4" t="n"/>
+      <c r="O139" s="4" t="n"/>
+      <c r="P139" s="4" t="n"/>
       <c r="Q139" s="4" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-03; 相对D0=2.09%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -10111,24 +7978,12 @@
       <c r="J140" s="4" t="n">
         <v>141.5</v>
       </c>
-      <c r="K140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P140" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K140" s="4" t="n"/>
+      <c r="L140" s="4" t="n"/>
+      <c r="M140" s="4" t="n"/>
+      <c r="N140" s="4" t="n"/>
+      <c r="O140" s="4" t="n"/>
+      <c r="P140" s="4" t="n"/>
       <c r="Q140" s="4" t="inlineStr">
         <is>
           <t>D0=136.62; 最新=2026-06-03; 相对D0=3.57%</t>
@@ -10180,24 +8035,6 @@
       <c r="J141" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K141" t="n">
-        <v/>
-      </c>
-      <c r="L141" t="n">
-        <v/>
-      </c>
-      <c r="M141" t="n">
-        <v/>
-      </c>
-      <c r="N141" t="n">
-        <v/>
-      </c>
-      <c r="O141" t="n">
-        <v/>
-      </c>
-      <c r="P141" t="n">
-        <v/>
-      </c>
       <c r="Q141" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-03; 相对D0=-8.58%</t>
@@ -10249,24 +8086,6 @@
       <c r="J142" t="n">
         <v>24.85</v>
       </c>
-      <c r="K142" t="n">
-        <v/>
-      </c>
-      <c r="L142" t="n">
-        <v/>
-      </c>
-      <c r="M142" t="n">
-        <v/>
-      </c>
-      <c r="N142" t="n">
-        <v/>
-      </c>
-      <c r="O142" t="n">
-        <v/>
-      </c>
-      <c r="P142" t="n">
-        <v/>
-      </c>
       <c r="Q142" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-03; 相对D0=-8.47%</t>
@@ -10318,24 +8137,6 @@
       <c r="J143" t="n">
         <v>50.01</v>
       </c>
-      <c r="K143" t="n">
-        <v/>
-      </c>
-      <c r="L143" t="n">
-        <v/>
-      </c>
-      <c r="M143" t="n">
-        <v/>
-      </c>
-      <c r="N143" t="n">
-        <v/>
-      </c>
-      <c r="O143" t="n">
-        <v/>
-      </c>
-      <c r="P143" t="n">
-        <v/>
-      </c>
       <c r="Q143" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-03; 相对D0=-1.07%</t>
@@ -10387,24 +8188,12 @@
       <c r="J144" s="4" t="n">
         <v>181.67</v>
       </c>
-      <c r="K144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O144" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P144" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K144" s="4" t="n"/>
+      <c r="L144" s="4" t="n"/>
+      <c r="M144" s="4" t="n"/>
+      <c r="N144" s="4" t="n"/>
+      <c r="O144" s="4" t="n"/>
+      <c r="P144" s="4" t="n"/>
       <c r="Q144" s="4" t="inlineStr">
         <is>
           <t>D0=189.00; 最新=2026-06-03; 相对D0=-3.88%</t>
@@ -10456,24 +8245,12 @@
       <c r="J145" s="4" t="n">
         <v>938</v>
       </c>
-      <c r="K145" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L145" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M145" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N145" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O145" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P145" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K145" s="4" t="n"/>
+      <c r="L145" s="4" t="n"/>
+      <c r="M145" s="4" t="n"/>
+      <c r="N145" s="4" t="n"/>
+      <c r="O145" s="4" t="n"/>
+      <c r="P145" s="4" t="n"/>
       <c r="Q145" s="4" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-03; 相对D0=3.65%</t>
@@ -10525,24 +8302,12 @@
       <c r="J146" s="4" t="n">
         <v>12.29</v>
       </c>
-      <c r="K146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O146" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P146" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K146" s="4" t="n"/>
+      <c r="L146" s="4" t="n"/>
+      <c r="M146" s="4" t="n"/>
+      <c r="N146" s="4" t="n"/>
+      <c r="O146" s="4" t="n"/>
+      <c r="P146" s="4" t="n"/>
       <c r="Q146" s="4" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-03; 相对D0=11.52%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -10594,24 +8359,6 @@
       <c r="J147" t="n">
         <v>214.75</v>
       </c>
-      <c r="K147" t="n">
-        <v/>
-      </c>
-      <c r="L147" t="n">
-        <v/>
-      </c>
-      <c r="M147" t="n">
-        <v/>
-      </c>
-      <c r="N147" t="n">
-        <v/>
-      </c>
-      <c r="O147" t="n">
-        <v/>
-      </c>
-      <c r="P147" t="n">
-        <v/>
-      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>D0=224.36; 最新=2026-06-03; 相对D0=-4.28%</t>
@@ -10663,24 +8410,12 @@
       <c r="J148" s="4" t="n">
         <v>65.20999999999999</v>
       </c>
-      <c r="K148" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L148" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M148" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N148" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O148" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P148" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K148" s="4" t="n"/>
+      <c r="L148" s="4" t="n"/>
+      <c r="M148" s="4" t="n"/>
+      <c r="N148" s="4" t="n"/>
+      <c r="O148" s="4" t="n"/>
+      <c r="P148" s="4" t="n"/>
       <c r="Q148" s="4" t="inlineStr">
         <is>
           <t>D0=66.89; 最新=2026-06-03; 相对D0=-2.51%</t>
@@ -10732,24 +8467,12 @@
       <c r="J149" s="4" t="n">
         <v>59.64</v>
       </c>
-      <c r="K149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P149" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K149" s="4" t="n"/>
+      <c r="L149" s="4" t="n"/>
+      <c r="M149" s="4" t="n"/>
+      <c r="N149" s="4" t="n"/>
+      <c r="O149" s="4" t="n"/>
+      <c r="P149" s="4" t="n"/>
       <c r="Q149" s="4" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-03; 相对D0=1.22%</t>
@@ -10801,24 +8524,12 @@
       <c r="J150" s="4" t="n">
         <v>15.38</v>
       </c>
-      <c r="K150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P150" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K150" s="4" t="n"/>
+      <c r="L150" s="4" t="n"/>
+      <c r="M150" s="4" t="n"/>
+      <c r="N150" s="4" t="n"/>
+      <c r="O150" s="4" t="n"/>
+      <c r="P150" s="4" t="n"/>
       <c r="Q150" s="4" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-03; 相对D0=10.73%</t>
@@ -10870,24 +8581,6 @@
       <c r="J151" t="n">
         <v>14.85</v>
       </c>
-      <c r="K151" t="n">
-        <v/>
-      </c>
-      <c r="L151" t="n">
-        <v/>
-      </c>
-      <c r="M151" t="n">
-        <v/>
-      </c>
-      <c r="N151" t="n">
-        <v/>
-      </c>
-      <c r="O151" t="n">
-        <v/>
-      </c>
-      <c r="P151" t="n">
-        <v/>
-      </c>
       <c r="Q151" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-03; 相对D0=-4.69%</t>
@@ -10939,24 +8632,12 @@
       <c r="J152" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="K152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P152" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K152" s="4" t="n"/>
+      <c r="L152" s="4" t="n"/>
+      <c r="M152" s="4" t="n"/>
+      <c r="N152" s="4" t="n"/>
+      <c r="O152" s="4" t="n"/>
+      <c r="P152" s="4" t="n"/>
       <c r="Q152" s="4" t="inlineStr">
         <is>
           <t>D0=17.62; 最新=2026-06-03; 相对D0=2.16%</t>
@@ -11008,24 +8689,6 @@
       <c r="J153" t="n">
         <v>331.44</v>
       </c>
-      <c r="K153" t="n">
-        <v/>
-      </c>
-      <c r="L153" t="n">
-        <v/>
-      </c>
-      <c r="M153" t="n">
-        <v/>
-      </c>
-      <c r="N153" t="n">
-        <v/>
-      </c>
-      <c r="O153" t="n">
-        <v/>
-      </c>
-      <c r="P153" t="n">
-        <v/>
-      </c>
       <c r="Q153" t="inlineStr">
         <is>
           <t>D0=323.39; 最新=2026-06-03; 相对D0=2.49%</t>
@@ -11077,24 +8740,6 @@
       <c r="J154" t="n">
         <v>134.37</v>
       </c>
-      <c r="K154" t="n">
-        <v/>
-      </c>
-      <c r="L154" t="n">
-        <v/>
-      </c>
-      <c r="M154" t="n">
-        <v/>
-      </c>
-      <c r="N154" t="n">
-        <v/>
-      </c>
-      <c r="O154" t="n">
-        <v/>
-      </c>
-      <c r="P154" t="n">
-        <v/>
-      </c>
       <c r="Q154" t="inlineStr">
         <is>
           <t>D0=155.71; 最新=2026-06-03; 相对D0=-13.70%</t>
@@ -11146,24 +8791,12 @@
       <c r="J155" s="4" t="n">
         <v>114.59</v>
       </c>
-      <c r="K155" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L155" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M155" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N155" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O155" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P155" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K155" s="4" t="n"/>
+      <c r="L155" s="4" t="n"/>
+      <c r="M155" s="4" t="n"/>
+      <c r="N155" s="4" t="n"/>
+      <c r="O155" s="4" t="n"/>
+      <c r="P155" s="4" t="n"/>
       <c r="Q155" s="4" t="inlineStr">
         <is>
           <t>D0=113.00; 最新=2026-06-03; 相对D0=1.41%</t>
@@ -11215,24 +8848,6 @@
       <c r="J156" t="n">
         <v>107.73</v>
       </c>
-      <c r="K156" t="n">
-        <v/>
-      </c>
-      <c r="L156" t="n">
-        <v/>
-      </c>
-      <c r="M156" t="n">
-        <v/>
-      </c>
-      <c r="N156" t="n">
-        <v/>
-      </c>
-      <c r="O156" t="n">
-        <v/>
-      </c>
-      <c r="P156" t="n">
-        <v/>
-      </c>
       <c r="Q156" t="inlineStr">
         <is>
           <t>D0=118.17; 最新=2026-06-03; 相对D0=-8.83%</t>
@@ -11284,24 +8899,6 @@
       <c r="J157" t="n">
         <v>287.32</v>
       </c>
-      <c r="K157" t="n">
-        <v/>
-      </c>
-      <c r="L157" t="n">
-        <v/>
-      </c>
-      <c r="M157" t="n">
-        <v/>
-      </c>
-      <c r="N157" t="n">
-        <v/>
-      </c>
-      <c r="O157" t="n">
-        <v/>
-      </c>
-      <c r="P157" t="n">
-        <v/>
-      </c>
       <c r="Q157" t="inlineStr">
         <is>
           <t>D0=302.85; 最新=2026-06-03; 相对D0=-5.13%</t>
@@ -11353,24 +8950,12 @@
       <c r="J158" s="4" t="n">
         <v>183.45</v>
       </c>
-      <c r="K158" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L158" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M158" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N158" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O158" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P158" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K158" s="4" t="n"/>
+      <c r="L158" s="4" t="n"/>
+      <c r="M158" s="4" t="n"/>
+      <c r="N158" s="4" t="n"/>
+      <c r="O158" s="4" t="n"/>
+      <c r="P158" s="4" t="n"/>
       <c r="Q158" s="4" t="inlineStr">
         <is>
           <t>D0=187.52; 最新=2026-06-03; 相对D0=-2.17%</t>
@@ -11422,24 +9007,12 @@
       <c r="J159" s="4" t="n">
         <v>417.43</v>
       </c>
-      <c r="K159" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L159" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M159" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N159" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O159" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P159" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K159" s="4" t="n"/>
+      <c r="L159" s="4" t="n"/>
+      <c r="M159" s="4" t="n"/>
+      <c r="N159" s="4" t="n"/>
+      <c r="O159" s="4" t="n"/>
+      <c r="P159" s="4" t="n"/>
       <c r="Q159" s="4" t="inlineStr">
         <is>
           <t>D0=426.89; 最新=2026-06-03; 相对D0=-2.22%</t>
@@ -11491,24 +9064,12 @@
       <c r="J160" s="4" t="n">
         <v>119.05</v>
       </c>
-      <c r="K160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P160" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K160" s="4" t="n"/>
+      <c r="L160" s="4" t="n"/>
+      <c r="M160" s="4" t="n"/>
+      <c r="N160" s="4" t="n"/>
+      <c r="O160" s="4" t="n"/>
+      <c r="P160" s="4" t="n"/>
       <c r="Q160" s="4" t="inlineStr">
         <is>
           <t>D0=116.87; 最新=2026-06-03; 相对D0=1.87%</t>
@@ -11560,24 +9121,12 @@
       <c r="J161" s="4" t="n">
         <v>214.6</v>
       </c>
-      <c r="K161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P161" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K161" s="4" t="n"/>
+      <c r="L161" s="4" t="n"/>
+      <c r="M161" s="4" t="n"/>
+      <c r="N161" s="4" t="n"/>
+      <c r="O161" s="4" t="n"/>
+      <c r="P161" s="4" t="n"/>
       <c r="Q161" s="4" t="inlineStr">
         <is>
           <t>D0=229.00; 最新=2026-06-03; 相对D0=-6.29%</t>
@@ -11629,24 +9178,12 @@
       <c r="J162" s="4" t="n">
         <v>189.71</v>
       </c>
-      <c r="K162" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L162" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M162" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N162" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O162" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P162" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K162" s="4" t="n"/>
+      <c r="L162" s="4" t="n"/>
+      <c r="M162" s="4" t="n"/>
+      <c r="N162" s="4" t="n"/>
+      <c r="O162" s="4" t="n"/>
+      <c r="P162" s="4" t="n"/>
       <c r="Q162" s="4" t="inlineStr">
         <is>
           <t>D0=187.55; 最新=2026-06-03; 相对D0=1.15%</t>
@@ -11698,24 +9235,6 @@
       <c r="J163" t="n">
         <v>65.45999999999999</v>
       </c>
-      <c r="K163" t="n">
-        <v/>
-      </c>
-      <c r="L163" t="n">
-        <v/>
-      </c>
-      <c r="M163" t="n">
-        <v/>
-      </c>
-      <c r="N163" t="n">
-        <v/>
-      </c>
-      <c r="O163" t="n">
-        <v/>
-      </c>
-      <c r="P163" t="n">
-        <v/>
-      </c>
       <c r="Q163" t="inlineStr">
         <is>
           <t>D0=66.47; 最新=2026-06-03; 相对D0=-1.52%</t>
@@ -11767,24 +9286,12 @@
       <c r="J164" s="4" t="n">
         <v>47.97</v>
       </c>
-      <c r="K164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P164" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K164" s="4" t="n"/>
+      <c r="L164" s="4" t="n"/>
+      <c r="M164" s="4" t="n"/>
+      <c r="N164" s="4" t="n"/>
+      <c r="O164" s="4" t="n"/>
+      <c r="P164" s="4" t="n"/>
       <c r="Q164" s="4" t="inlineStr">
         <is>
           <t>D0=48.66; 最新=2026-06-03; 相对D0=-1.42%</t>
@@ -11836,24 +9343,6 @@
       <c r="J165" t="n">
         <v>69.02</v>
       </c>
-      <c r="K165" t="n">
-        <v/>
-      </c>
-      <c r="L165" t="n">
-        <v/>
-      </c>
-      <c r="M165" t="n">
-        <v/>
-      </c>
-      <c r="N165" t="n">
-        <v/>
-      </c>
-      <c r="O165" t="n">
-        <v/>
-      </c>
-      <c r="P165" t="n">
-        <v/>
-      </c>
       <c r="Q165" t="inlineStr">
         <is>
           <t>D0=72.33; 最新=2026-06-03; 相对D0=-4.58%</t>
@@ -11905,24 +9394,12 @@
       <c r="J166" s="4" t="n">
         <v>140.33</v>
       </c>
-      <c r="K166" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L166" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M166" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N166" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O166" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P166" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K166" s="4" t="n"/>
+      <c r="L166" s="4" t="n"/>
+      <c r="M166" s="4" t="n"/>
+      <c r="N166" s="4" t="n"/>
+      <c r="O166" s="4" t="n"/>
+      <c r="P166" s="4" t="n"/>
       <c r="Q166" s="4" t="inlineStr">
         <is>
           <t>D0=142.92; 最新=2026-06-03; 相对D0=-1.81%</t>
@@ -11974,24 +9451,12 @@
       <c r="J167" s="4" t="n">
         <v>141.5</v>
       </c>
-      <c r="K167" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L167" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M167" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N167" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O167" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P167" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K167" s="4" t="n"/>
+      <c r="L167" s="4" t="n"/>
+      <c r="M167" s="4" t="n"/>
+      <c r="N167" s="4" t="n"/>
+      <c r="O167" s="4" t="n"/>
+      <c r="P167" s="4" t="n"/>
       <c r="Q167" s="4" t="inlineStr">
         <is>
           <t>D0=138.58; 最新=2026-06-03; 相对D0=2.11%</t>
@@ -12043,24 +9508,12 @@
       <c r="J168" s="4" t="n">
         <v>421.21</v>
       </c>
-      <c r="K168" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L168" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M168" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N168" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O168" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P168" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K168" s="4" t="n"/>
+      <c r="L168" s="4" t="n"/>
+      <c r="M168" s="4" t="n"/>
+      <c r="N168" s="4" t="n"/>
+      <c r="O168" s="4" t="n"/>
+      <c r="P168" s="4" t="n"/>
       <c r="Q168" s="4" t="inlineStr">
         <is>
           <t>D0=417.62; 最新=2026-06-03; 相对D0=0.86%</t>
@@ -12112,24 +9565,12 @@
       <c r="J169" s="4" t="n">
         <v>200.76</v>
       </c>
-      <c r="K169" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L169" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M169" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N169" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O169" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P169" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K169" s="4" t="n"/>
+      <c r="L169" s="4" t="n"/>
+      <c r="M169" s="4" t="n"/>
+      <c r="N169" s="4" t="n"/>
+      <c r="O169" s="4" t="n"/>
+      <c r="P169" s="4" t="n"/>
       <c r="Q169" s="4" t="inlineStr">
         <is>
           <t>D0=200.40; 最新=2026-06-03; 相对D0=0.18%</t>
@@ -12181,24 +9622,12 @@
       <c r="J170" s="4" t="n">
         <v>12.29</v>
       </c>
-      <c r="K170" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L170" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M170" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N170" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O170" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P170" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K170" s="4" t="n"/>
+      <c r="L170" s="4" t="n"/>
+      <c r="M170" s="4" t="n"/>
+      <c r="N170" s="4" t="n"/>
+      <c r="O170" s="4" t="n"/>
+      <c r="P170" s="4" t="n"/>
       <c r="Q170" s="4" t="inlineStr">
         <is>
           <t>D0=12.72; 最新=2026-06-03; 相对D0=-3.38%</t>
@@ -12250,24 +9679,6 @@
       <c r="J171" t="n">
         <v>11.1</v>
       </c>
-      <c r="K171" t="n">
-        <v/>
-      </c>
-      <c r="L171" t="n">
-        <v/>
-      </c>
-      <c r="M171" t="n">
-        <v/>
-      </c>
-      <c r="N171" t="n">
-        <v/>
-      </c>
-      <c r="O171" t="n">
-        <v/>
-      </c>
-      <c r="P171" t="n">
-        <v/>
-      </c>
       <c r="Q171" t="inlineStr">
         <is>
           <t>D0=11.72; 最新=2026-06-03; 相对D0=-5.29%</t>
@@ -12319,24 +9730,6 @@
       <c r="J172" t="n">
         <v>23.3</v>
       </c>
-      <c r="K172" t="n">
-        <v/>
-      </c>
-      <c r="L172" t="n">
-        <v/>
-      </c>
-      <c r="M172" t="n">
-        <v/>
-      </c>
-      <c r="N172" t="n">
-        <v/>
-      </c>
-      <c r="O172" t="n">
-        <v/>
-      </c>
-      <c r="P172" t="n">
-        <v/>
-      </c>
       <c r="Q172" t="inlineStr">
         <is>
           <t>D0=23.30; 最新=2026-06-03; 相对D0=0.00%</t>
@@ -12388,24 +9781,12 @@
       <c r="J173" s="4" t="n">
         <v>131.83</v>
       </c>
-      <c r="K173" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L173" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M173" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N173" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O173" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P173" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K173" s="4" t="n"/>
+      <c r="L173" s="4" t="n"/>
+      <c r="M173" s="4" t="n"/>
+      <c r="N173" s="4" t="n"/>
+      <c r="O173" s="4" t="n"/>
+      <c r="P173" s="4" t="n"/>
       <c r="Q173" s="4" t="inlineStr">
         <is>
           <t>D0=138.17; 最新=2026-06-03; 相对D0=-4.59%</t>
@@ -12457,24 +9838,12 @@
       <c r="J174" s="4" t="n">
         <v>133.76</v>
       </c>
-      <c r="K174" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L174" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M174" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N174" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O174" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P174" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K174" s="4" t="n"/>
+      <c r="L174" s="4" t="n"/>
+      <c r="M174" s="4" t="n"/>
+      <c r="N174" s="4" t="n"/>
+      <c r="O174" s="4" t="n"/>
+      <c r="P174" s="4" t="n"/>
       <c r="Q174" s="4" t="inlineStr">
         <is>
           <t>D0=133.51; 最新=2026-06-03; 相对D0=0.19%</t>
@@ -12526,24 +9895,12 @@
       <c r="J175" s="4" t="n">
         <v>65.20999999999999</v>
       </c>
-      <c r="K175" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L175" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M175" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N175" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O175" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P175" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K175" s="4" t="n"/>
+      <c r="L175" s="4" t="n"/>
+      <c r="M175" s="4" t="n"/>
+      <c r="N175" s="4" t="n"/>
+      <c r="O175" s="4" t="n"/>
+      <c r="P175" s="4" t="n"/>
       <c r="Q175" s="4" t="inlineStr">
         <is>
           <t>D0=73.47; 最新=2026-06-03; 相对D0=-11.24%</t>
@@ -12595,24 +9952,12 @@
       <c r="J176" s="4" t="n">
         <v>279.98</v>
       </c>
-      <c r="K176" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L176" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M176" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N176" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O176" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P176" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K176" s="4" t="n"/>
+      <c r="L176" s="4" t="n"/>
+      <c r="M176" s="4" t="n"/>
+      <c r="N176" s="4" t="n"/>
+      <c r="O176" s="4" t="n"/>
+      <c r="P176" s="4" t="n"/>
       <c r="Q176" s="4" t="inlineStr">
         <is>
           <t>D0=278.02; 最新=2026-06-03; 相对D0=0.70%</t>
@@ -12664,24 +10009,6 @@
       <c r="J177" t="n">
         <v>57.29</v>
       </c>
-      <c r="K177" t="n">
-        <v/>
-      </c>
-      <c r="L177" t="n">
-        <v/>
-      </c>
-      <c r="M177" t="n">
-        <v/>
-      </c>
-      <c r="N177" t="n">
-        <v/>
-      </c>
-      <c r="O177" t="n">
-        <v/>
-      </c>
-      <c r="P177" t="n">
-        <v/>
-      </c>
       <c r="Q177" t="inlineStr">
         <is>
           <t>D0=56.89; 最新=2026-06-03; 相对D0=0.70%</t>
@@ -12733,24 +10060,12 @@
       <c r="J178" s="4" t="n">
         <v>56.85</v>
       </c>
-      <c r="K178" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L178" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M178" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N178" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O178" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P178" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K178" s="4" t="n"/>
+      <c r="L178" s="4" t="n"/>
+      <c r="M178" s="4" t="n"/>
+      <c r="N178" s="4" t="n"/>
+      <c r="O178" s="4" t="n"/>
+      <c r="P178" s="4" t="n"/>
       <c r="Q178" s="4" t="inlineStr">
         <is>
           <t>D0=56.56; 最新=2026-06-03; 相对D0=0.51%</t>
@@ -12802,24 +10117,6 @@
       <c r="J179" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="K179" t="n">
-        <v/>
-      </c>
-      <c r="L179" t="n">
-        <v/>
-      </c>
-      <c r="M179" t="n">
-        <v/>
-      </c>
-      <c r="N179" t="n">
-        <v/>
-      </c>
-      <c r="O179" t="n">
-        <v/>
-      </c>
-      <c r="P179" t="n">
-        <v/>
-      </c>
       <c r="Q179" t="inlineStr">
         <is>
           <t>D0=87.39; 最新=2026-06-03; 相对D0=-0.90%</t>
@@ -12871,24 +10168,12 @@
       <c r="J180" s="4" t="n">
         <v>409.67</v>
       </c>
-      <c r="K180" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L180" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M180" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N180" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O180" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P180" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K180" s="4" t="n"/>
+      <c r="L180" s="4" t="n"/>
+      <c r="M180" s="4" t="n"/>
+      <c r="N180" s="4" t="n"/>
+      <c r="O180" s="4" t="n"/>
+      <c r="P180" s="4" t="n"/>
       <c r="Q180" s="4" t="inlineStr">
         <is>
           <t>D0=392.62; 最新=2026-06-03; 相对D0=4.34%</t>
@@ -12940,24 +10225,12 @@
       <c r="J181" s="4" t="n">
         <v>379.59</v>
       </c>
-      <c r="K181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P181" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K181" s="4" t="n"/>
+      <c r="L181" s="4" t="n"/>
+      <c r="M181" s="4" t="n"/>
+      <c r="N181" s="4" t="n"/>
+      <c r="O181" s="4" t="n"/>
+      <c r="P181" s="4" t="n"/>
       <c r="Q181" s="4" t="inlineStr">
         <is>
           <t>D0=385.51; 最新=2026-06-03; 相对D0=-1.54%</t>
@@ -13009,24 +10282,12 @@
       <c r="J182" s="4" t="n">
         <v>14.09</v>
       </c>
-      <c r="K182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P182" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K182" s="4" t="n"/>
+      <c r="L182" s="4" t="n"/>
+      <c r="M182" s="4" t="n"/>
+      <c r="N182" s="4" t="n"/>
+      <c r="O182" s="4" t="n"/>
+      <c r="P182" s="4" t="n"/>
       <c r="Q182" s="4" t="inlineStr">
         <is>
           <t>D0=15.44; 最新=2026-06-03; 相对D0=-8.74%</t>
@@ -13078,24 +10339,12 @@
       <c r="J183" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="K183" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L183" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M183" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N183" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O183" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P183" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K183" s="4" t="n"/>
+      <c r="L183" s="4" t="n"/>
+      <c r="M183" s="4" t="n"/>
+      <c r="N183" s="4" t="n"/>
+      <c r="O183" s="4" t="n"/>
+      <c r="P183" s="4" t="n"/>
       <c r="Q183" s="4" t="inlineStr">
         <is>
           <t>D0=19.54; 最新=2026-06-03; 相对D0=-7.88%</t>
@@ -13147,24 +10396,6 @@
       <c r="J184" t="n">
         <v>331.44</v>
       </c>
-      <c r="K184" t="n">
-        <v/>
-      </c>
-      <c r="L184" t="n">
-        <v/>
-      </c>
-      <c r="M184" t="n">
-        <v/>
-      </c>
-      <c r="N184" t="n">
-        <v/>
-      </c>
-      <c r="O184" t="n">
-        <v/>
-      </c>
-      <c r="P184" t="n">
-        <v/>
-      </c>
       <c r="Q184" t="inlineStr">
         <is>
           <t>D0=334.49; 最新=2026-06-03; 相对D0=-0.91%</t>
@@ -13216,24 +10447,12 @@
       <c r="J185" s="4" t="n">
         <v>153.8</v>
       </c>
-      <c r="K185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O185" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P185" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K185" s="4" t="n"/>
+      <c r="L185" s="4" t="n"/>
+      <c r="M185" s="4" t="n"/>
+      <c r="N185" s="4" t="n"/>
+      <c r="O185" s="4" t="n"/>
+      <c r="P185" s="4" t="n"/>
       <c r="Q185" s="4" t="inlineStr">
         <is>
           <t>D0=157.97; 最新=2026-06-03; 相对D0=-2.64%</t>
@@ -13285,24 +10504,6 @@
       <c r="J186" t="n">
         <v>51.63</v>
       </c>
-      <c r="K186" t="n">
-        <v/>
-      </c>
-      <c r="L186" t="n">
-        <v/>
-      </c>
-      <c r="M186" t="n">
-        <v/>
-      </c>
-      <c r="N186" t="n">
-        <v/>
-      </c>
-      <c r="O186" t="n">
-        <v/>
-      </c>
-      <c r="P186" t="n">
-        <v/>
-      </c>
       <c r="Q186" t="inlineStr">
         <is>
           <t>D0=51.52; 最新=2026-06-03; 相对D0=0.21%</t>
@@ -13354,24 +10555,6 @@
       <c r="J187" t="n">
         <v>50.87</v>
       </c>
-      <c r="K187" t="n">
-        <v/>
-      </c>
-      <c r="L187" t="n">
-        <v/>
-      </c>
-      <c r="M187" t="n">
-        <v/>
-      </c>
-      <c r="N187" t="n">
-        <v/>
-      </c>
-      <c r="O187" t="n">
-        <v/>
-      </c>
-      <c r="P187" t="n">
-        <v/>
-      </c>
       <c r="Q187" t="inlineStr">
         <is>
           <t>D0=51.46; 最新=2026-06-03; 相对D0=-1.15%</t>
@@ -13423,24 +10606,12 @@
       <c r="J188" s="4" t="n">
         <v>43.71</v>
       </c>
-      <c r="K188" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L188" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M188" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N188" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O188" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P188" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K188" s="4" t="n"/>
+      <c r="L188" s="4" t="n"/>
+      <c r="M188" s="4" t="n"/>
+      <c r="N188" s="4" t="n"/>
+      <c r="O188" s="4" t="n"/>
+      <c r="P188" s="4" t="n"/>
       <c r="Q188" s="4" t="inlineStr">
         <is>
           <t>D0=43.71; 最新=2026-06-03; 相对D0=0.00%</t>
@@ -13677,24 +10848,6 @@
       <c r="J200" t="n">
         <v>44.71</v>
       </c>
-      <c r="K200" t="n">
-        <v/>
-      </c>
-      <c r="L200" t="n">
-        <v/>
-      </c>
-      <c r="M200" t="n">
-        <v/>
-      </c>
-      <c r="N200" t="n">
-        <v/>
-      </c>
-      <c r="O200" t="n">
-        <v/>
-      </c>
-      <c r="P200" t="n">
-        <v/>
-      </c>
       <c r="Q200" t="inlineStr">
         <is>
           <t>D0=44.71; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13746,24 +10899,6 @@
       <c r="J201" t="n">
         <v>16.42</v>
       </c>
-      <c r="K201" t="n">
-        <v/>
-      </c>
-      <c r="L201" t="n">
-        <v/>
-      </c>
-      <c r="M201" t="n">
-        <v/>
-      </c>
-      <c r="N201" t="n">
-        <v/>
-      </c>
-      <c r="O201" t="n">
-        <v/>
-      </c>
-      <c r="P201" t="n">
-        <v/>
-      </c>
       <c r="Q201" t="inlineStr">
         <is>
           <t>D0=16.42; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警卖出)</t>
@@ -13815,24 +10950,12 @@
       <c r="J202" s="4" t="n">
         <v>214.6</v>
       </c>
-      <c r="K202" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L202" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M202" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N202" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O202" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P202" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K202" s="4" t="n"/>
+      <c r="L202" s="4" t="n"/>
+      <c r="M202" s="4" t="n"/>
+      <c r="N202" s="4" t="n"/>
+      <c r="O202" s="4" t="n"/>
+      <c r="P202" s="4" t="n"/>
       <c r="Q202" s="4" t="inlineStr">
         <is>
           <t>D0=214.60; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -13884,24 +11007,6 @@
       <c r="J203" t="n">
         <v>110.93</v>
       </c>
-      <c r="K203" t="n">
-        <v/>
-      </c>
-      <c r="L203" t="n">
-        <v/>
-      </c>
-      <c r="M203" t="n">
-        <v/>
-      </c>
-      <c r="N203" t="n">
-        <v/>
-      </c>
-      <c r="O203" t="n">
-        <v/>
-      </c>
-      <c r="P203" t="n">
-        <v/>
-      </c>
       <c r="Q203" t="inlineStr">
         <is>
           <t>D0=110.93; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13953,24 +11058,6 @@
       <c r="J204" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K204" t="n">
-        <v/>
-      </c>
-      <c r="L204" t="n">
-        <v/>
-      </c>
-      <c r="M204" t="n">
-        <v/>
-      </c>
-      <c r="N204" t="n">
-        <v/>
-      </c>
-      <c r="O204" t="n">
-        <v/>
-      </c>
-      <c r="P204" t="n">
-        <v/>
-      </c>
       <c r="Q204" t="inlineStr">
         <is>
           <t>D0=8.20; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14022,24 +11109,6 @@
       <c r="J205" t="n">
         <v>82.84999999999999</v>
       </c>
-      <c r="K205" t="n">
-        <v/>
-      </c>
-      <c r="L205" t="n">
-        <v/>
-      </c>
-      <c r="M205" t="n">
-        <v/>
-      </c>
-      <c r="N205" t="n">
-        <v/>
-      </c>
-      <c r="O205" t="n">
-        <v/>
-      </c>
-      <c r="P205" t="n">
-        <v/>
-      </c>
       <c r="Q205" t="inlineStr">
         <is>
           <t>D0=82.85; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14091,24 +11160,6 @@
       <c r="J206" t="n">
         <v>427.34</v>
       </c>
-      <c r="K206" t="n">
-        <v/>
-      </c>
-      <c r="L206" t="n">
-        <v/>
-      </c>
-      <c r="M206" t="n">
-        <v/>
-      </c>
-      <c r="N206" t="n">
-        <v/>
-      </c>
-      <c r="O206" t="n">
-        <v/>
-      </c>
-      <c r="P206" t="n">
-        <v/>
-      </c>
       <c r="Q206" t="inlineStr">
         <is>
           <t>D0=427.34; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14160,24 +11211,12 @@
       <c r="J207" s="4" t="n">
         <v>26.37</v>
       </c>
-      <c r="K207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O207" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P207" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K207" s="4" t="n"/>
+      <c r="L207" s="4" t="n"/>
+      <c r="M207" s="4" t="n"/>
+      <c r="N207" s="4" t="n"/>
+      <c r="O207" s="4" t="n"/>
+      <c r="P207" s="4" t="n"/>
       <c r="Q207" s="4" t="inlineStr">
         <is>
           <t>D0=26.37; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14229,24 +11268,12 @@
       <c r="J208" s="4" t="n">
         <v>65.20999999999999</v>
       </c>
-      <c r="K208" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L208" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M208" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N208" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O208" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P208" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K208" s="4" t="n"/>
+      <c r="L208" s="4" t="n"/>
+      <c r="M208" s="4" t="n"/>
+      <c r="N208" s="4" t="n"/>
+      <c r="O208" s="4" t="n"/>
+      <c r="P208" s="4" t="n"/>
       <c r="Q208" s="4" t="inlineStr">
         <is>
           <t>D0=65.21; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -14298,24 +11325,6 @@
       <c r="J209" t="n">
         <v>142.2</v>
       </c>
-      <c r="K209" t="n">
-        <v/>
-      </c>
-      <c r="L209" t="n">
-        <v/>
-      </c>
-      <c r="M209" t="n">
-        <v/>
-      </c>
-      <c r="N209" t="n">
-        <v/>
-      </c>
-      <c r="O209" t="n">
-        <v/>
-      </c>
-      <c r="P209" t="n">
-        <v/>
-      </c>
       <c r="Q209" t="inlineStr">
         <is>
           <t>D0=142.20; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14367,24 +11376,6 @@
       <c r="J210" t="n">
         <v>14.85</v>
       </c>
-      <c r="K210" t="n">
-        <v/>
-      </c>
-      <c r="L210" t="n">
-        <v/>
-      </c>
-      <c r="M210" t="n">
-        <v/>
-      </c>
-      <c r="N210" t="n">
-        <v/>
-      </c>
-      <c r="O210" t="n">
-        <v/>
-      </c>
-      <c r="P210" t="n">
-        <v/>
-      </c>
       <c r="Q210" t="inlineStr">
         <is>
           <t>D0=14.85; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -14436,24 +11427,12 @@
       <c r="J211" s="4" t="n">
         <v>12.27</v>
       </c>
-      <c r="K211" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L211" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M211" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N211" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O211" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P211" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K211" s="4" t="n"/>
+      <c r="L211" s="4" t="n"/>
+      <c r="M211" s="4" t="n"/>
+      <c r="N211" s="4" t="n"/>
+      <c r="O211" s="4" t="n"/>
+      <c r="P211" s="4" t="n"/>
       <c r="Q211" s="4" t="inlineStr">
         <is>
           <t>D0=12.27; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14505,24 +11484,6 @@
       <c r="J212" t="n">
         <v>16.68</v>
       </c>
-      <c r="K212" t="n">
-        <v/>
-      </c>
-      <c r="L212" t="n">
-        <v/>
-      </c>
-      <c r="M212" t="n">
-        <v/>
-      </c>
-      <c r="N212" t="n">
-        <v/>
-      </c>
-      <c r="O212" t="n">
-        <v/>
-      </c>
-      <c r="P212" t="n">
-        <v/>
-      </c>
       <c r="Q212" t="inlineStr">
         <is>
           <t>D0=16.68; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14574,24 +11535,12 @@
       <c r="J213" s="4" t="n">
         <v>153.8</v>
       </c>
-      <c r="K213" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L213" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M213" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N213" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O213" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P213" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K213" s="4" t="n"/>
+      <c r="L213" s="4" t="n"/>
+      <c r="M213" s="4" t="n"/>
+      <c r="N213" s="4" t="n"/>
+      <c r="O213" s="4" t="n"/>
+      <c r="P213" s="4" t="n"/>
       <c r="Q213" s="4" t="inlineStr">
         <is>
           <t>D0=153.80; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -14643,24 +11592,12 @@
       <c r="J214" s="4" t="n">
         <v>41.03</v>
       </c>
-      <c r="K214" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L214" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M214" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N214" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O214" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P214" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K214" s="4" t="n"/>
+      <c r="L214" s="4" t="n"/>
+      <c r="M214" s="4" t="n"/>
+      <c r="N214" s="4" t="n"/>
+      <c r="O214" s="4" t="n"/>
+      <c r="P214" s="4" t="n"/>
       <c r="Q214" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-03; 相对D0=-1.06%</t>
@@ -14681,7 +11618,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -14708,24 +11644,6 @@
       <c r="J215" t="n">
         <v>88.62</v>
       </c>
-      <c r="K215" t="n">
-        <v/>
-      </c>
-      <c r="L215" t="n">
-        <v/>
-      </c>
-      <c r="M215" t="n">
-        <v/>
-      </c>
-      <c r="N215" t="n">
-        <v/>
-      </c>
-      <c r="O215" t="n">
-        <v/>
-      </c>
-      <c r="P215" t="n">
-        <v/>
-      </c>
       <c r="Q215" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-03; 相对D0=-2.23%</t>
@@ -14777,24 +11695,12 @@
       <c r="J216" s="4" t="n">
         <v>189.71</v>
       </c>
-      <c r="K216" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L216" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M216" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N216" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O216" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P216" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K216" s="4" t="n"/>
+      <c r="L216" s="4" t="n"/>
+      <c r="M216" s="4" t="n"/>
+      <c r="N216" s="4" t="n"/>
+      <c r="O216" s="4" t="n"/>
+      <c r="P216" s="4" t="n"/>
       <c r="Q216" s="4" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-03; 相对D0=2.71%</t>
@@ -14846,24 +11752,12 @@
       <c r="J217" s="4" t="n">
         <v>141.5</v>
       </c>
-      <c r="K217" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L217" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M217" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N217" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O217" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P217" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K217" s="4" t="n"/>
+      <c r="L217" s="4" t="n"/>
+      <c r="M217" s="4" t="n"/>
+      <c r="N217" s="4" t="n"/>
+      <c r="O217" s="4" t="n"/>
+      <c r="P217" s="4" t="n"/>
       <c r="Q217" s="4" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-03; 相对D0=3.89%</t>
@@ -14915,24 +11809,6 @@
       <c r="J218" t="n">
         <v>368.32</v>
       </c>
-      <c r="K218" t="n">
-        <v/>
-      </c>
-      <c r="L218" t="n">
-        <v/>
-      </c>
-      <c r="M218" t="n">
-        <v/>
-      </c>
-      <c r="N218" t="n">
-        <v/>
-      </c>
-      <c r="O218" t="n">
-        <v/>
-      </c>
-      <c r="P218" t="n">
-        <v/>
-      </c>
       <c r="Q218" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-03; 相对D0=19.84%</t>
@@ -14984,24 +11860,12 @@
       <c r="J219" s="4" t="n">
         <v>59.64</v>
       </c>
-      <c r="K219" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L219" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M219" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N219" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O219" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P219" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K219" s="4" t="n"/>
+      <c r="L219" s="4" t="n"/>
+      <c r="M219" s="4" t="n"/>
+      <c r="N219" s="4" t="n"/>
+      <c r="O219" s="4" t="n"/>
+      <c r="P219" s="4" t="n"/>
       <c r="Q219" s="4" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-03; 相对D0=3.79%</t>
@@ -15053,24 +11917,12 @@
       <c r="J220" s="4" t="n">
         <v>15.38</v>
       </c>
-      <c r="K220" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L220" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M220" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N220" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O220" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P220" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K220" s="4" t="n"/>
+      <c r="L220" s="4" t="n"/>
+      <c r="M220" s="4" t="n"/>
+      <c r="N220" s="4" t="n"/>
+      <c r="O220" s="4" t="n"/>
+      <c r="P220" s="4" t="n"/>
       <c r="Q220" s="4" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-03; 相对D0=15.21%</t>
@@ -15122,24 +11974,12 @@
       <c r="J221" s="4" t="n">
         <v>58.71</v>
       </c>
-      <c r="K221" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L221" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M221" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N221" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O221" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P221" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K221" s="4" t="n"/>
+      <c r="L221" s="4" t="n"/>
+      <c r="M221" s="4" t="n"/>
+      <c r="N221" s="4" t="n"/>
+      <c r="O221" s="4" t="n"/>
+      <c r="P221" s="4" t="n"/>
       <c r="Q221" s="4" t="inlineStr">
         <is>
           <t>D0=57.85; 最新=2026-06-03; 相对D0=1.49%</t>
@@ -15191,24 +12031,12 @@
       <c r="J222" s="4" t="n">
         <v>56.85</v>
       </c>
-      <c r="K222" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L222" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M222" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N222" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O222" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P222" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K222" s="4" t="n"/>
+      <c r="L222" s="4" t="n"/>
+      <c r="M222" s="4" t="n"/>
+      <c r="N222" s="4" t="n"/>
+      <c r="O222" s="4" t="n"/>
+      <c r="P222" s="4" t="n"/>
       <c r="Q222" s="4" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-03; 相对D0=0.62%</t>
@@ -15260,24 +12088,6 @@
       <c r="J223" t="n">
         <v>134.37</v>
       </c>
-      <c r="K223" t="n">
-        <v/>
-      </c>
-      <c r="L223" t="n">
-        <v/>
-      </c>
-      <c r="M223" t="n">
-        <v/>
-      </c>
-      <c r="N223" t="n">
-        <v/>
-      </c>
-      <c r="O223" t="n">
-        <v/>
-      </c>
-      <c r="P223" t="n">
-        <v/>
-      </c>
       <c r="Q223" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-03; 相对D0=6.30%</t>
@@ -15329,24 +12139,12 @@
       <c r="J224" s="4" t="n">
         <v>106.7</v>
       </c>
-      <c r="K224" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L224" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M224" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N224" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O224" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P224" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K224" s="4" t="n"/>
+      <c r="L224" s="4" t="n"/>
+      <c r="M224" s="4" t="n"/>
+      <c r="N224" s="4" t="n"/>
+      <c r="O224" s="4" t="n"/>
+      <c r="P224" s="4" t="n"/>
       <c r="Q224" s="4" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-03; 相对D0=-7.78%</t>
@@ -15398,24 +12196,12 @@
       <c r="J225" s="4" t="n">
         <v>267.24</v>
       </c>
-      <c r="K225" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L225" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M225" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N225" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O225" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P225" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K225" s="4" t="n"/>
+      <c r="L225" s="4" t="n"/>
+      <c r="M225" s="4" t="n"/>
+      <c r="N225" s="4" t="n"/>
+      <c r="O225" s="4" t="n"/>
+      <c r="P225" s="4" t="n"/>
       <c r="Q225" s="4" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-03; 相对D0=-6.66%</t>
@@ -15467,24 +12253,12 @@
       <c r="J226" s="4" t="n">
         <v>200.76</v>
       </c>
-      <c r="K226" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L226" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M226" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N226" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O226" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P226" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K226" s="4" t="n"/>
+      <c r="L226" s="4" t="n"/>
+      <c r="M226" s="4" t="n"/>
+      <c r="N226" s="4" t="n"/>
+      <c r="O226" s="4" t="n"/>
+      <c r="P226" s="4" t="n"/>
       <c r="Q226" s="4" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-03; 相对D0=9.72%</t>
@@ -15536,24 +12310,6 @@
       <c r="J227" t="n">
         <v>498.02</v>
       </c>
-      <c r="K227" t="n">
-        <v/>
-      </c>
-      <c r="L227" t="n">
-        <v/>
-      </c>
-      <c r="M227" t="n">
-        <v/>
-      </c>
-      <c r="N227" t="n">
-        <v/>
-      </c>
-      <c r="O227" t="n">
-        <v/>
-      </c>
-      <c r="P227" t="n">
-        <v/>
-      </c>
       <c r="Q227" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-03; 相对D0=3.62%</t>
@@ -15605,24 +12361,12 @@
       <c r="J228" s="4" t="n">
         <v>114.59</v>
       </c>
-      <c r="K228" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L228" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M228" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N228" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O228" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P228" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K228" s="4" t="n"/>
+      <c r="L228" s="4" t="n"/>
+      <c r="M228" s="4" t="n"/>
+      <c r="N228" s="4" t="n"/>
+      <c r="O228" s="4" t="n"/>
+      <c r="P228" s="4" t="n"/>
       <c r="Q228" s="4" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-03; 相对D0=24.11%</t>
@@ -15674,24 +12418,12 @@
       <c r="J229" s="4" t="n">
         <v>75.2</v>
       </c>
-      <c r="K229" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L229" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M229" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N229" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O229" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P229" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K229" s="4" t="n"/>
+      <c r="L229" s="4" t="n"/>
+      <c r="M229" s="4" t="n"/>
+      <c r="N229" s="4" t="n"/>
+      <c r="O229" s="4" t="n"/>
+      <c r="P229" s="4" t="n"/>
       <c r="Q229" s="4" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-03; 相对D0=8.11%</t>
@@ -15743,24 +12475,6 @@
       <c r="J230" t="n">
         <v>287.32</v>
       </c>
-      <c r="K230" t="n">
-        <v/>
-      </c>
-      <c r="L230" t="n">
-        <v/>
-      </c>
-      <c r="M230" t="n">
-        <v/>
-      </c>
-      <c r="N230" t="n">
-        <v/>
-      </c>
-      <c r="O230" t="n">
-        <v/>
-      </c>
-      <c r="P230" t="n">
-        <v/>
-      </c>
       <c r="Q230" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-03; 相对D0=0.81%</t>
@@ -15812,24 +12526,12 @@
       <c r="J231" s="4" t="n">
         <v>183.45</v>
       </c>
-      <c r="K231" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L231" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M231" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N231" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O231" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P231" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K231" s="4" t="n"/>
+      <c r="L231" s="4" t="n"/>
+      <c r="M231" s="4" t="n"/>
+      <c r="N231" s="4" t="n"/>
+      <c r="O231" s="4" t="n"/>
+      <c r="P231" s="4" t="n"/>
       <c r="Q231" s="4" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-03; 相对D0=6.87%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -15881,24 +12583,12 @@
       <c r="J232" s="4" t="n">
         <v>417.43</v>
       </c>
-      <c r="K232" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L232" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M232" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N232" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O232" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P232" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K232" s="4" t="n"/>
+      <c r="L232" s="4" t="n"/>
+      <c r="M232" s="4" t="n"/>
+      <c r="N232" s="4" t="n"/>
+      <c r="O232" s="4" t="n"/>
+      <c r="P232" s="4" t="n"/>
       <c r="Q232" s="4" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-03; 相对D0=15.48%</t>
@@ -15950,24 +12640,6 @@
       <c r="J233" t="n">
         <v>24.85</v>
       </c>
-      <c r="K233" t="n">
-        <v/>
-      </c>
-      <c r="L233" t="n">
-        <v/>
-      </c>
-      <c r="M233" t="n">
-        <v/>
-      </c>
-      <c r="N233" t="n">
-        <v/>
-      </c>
-      <c r="O233" t="n">
-        <v/>
-      </c>
-      <c r="P233" t="n">
-        <v/>
-      </c>
       <c r="Q233" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-03; 相对D0=31.62%</t>
@@ -16019,24 +12691,6 @@
       <c r="J234" t="n">
         <v>112.71</v>
       </c>
-      <c r="K234" t="n">
-        <v/>
-      </c>
-      <c r="L234" t="n">
-        <v/>
-      </c>
-      <c r="M234" t="n">
-        <v/>
-      </c>
-      <c r="N234" t="n">
-        <v/>
-      </c>
-      <c r="O234" t="n">
-        <v/>
-      </c>
-      <c r="P234" t="n">
-        <v/>
-      </c>
       <c r="Q234" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-03; 相对D0=-1.72%</t>
@@ -16088,24 +12742,12 @@
       <c r="J235" s="4" t="n">
         <v>133.76</v>
       </c>
-      <c r="K235" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L235" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M235" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N235" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O235" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P235" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K235" s="4" t="n"/>
+      <c r="L235" s="4" t="n"/>
+      <c r="M235" s="4" t="n"/>
+      <c r="N235" s="4" t="n"/>
+      <c r="O235" s="4" t="n"/>
+      <c r="P235" s="4" t="n"/>
       <c r="Q235" s="4" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-03; 相对D0=-0.24%</t>
@@ -16157,24 +12799,12 @@
       <c r="J236" s="4" t="n">
         <v>267.91</v>
       </c>
-      <c r="K236" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L236" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M236" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N236" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O236" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P236" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K236" s="4" t="n"/>
+      <c r="L236" s="4" t="n"/>
+      <c r="M236" s="4" t="n"/>
+      <c r="N236" s="4" t="n"/>
+      <c r="O236" s="4" t="n"/>
+      <c r="P236" s="4" t="n"/>
       <c r="Q236" s="4" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-03; 相对D0=4.97%</t>
@@ -16226,24 +12856,6 @@
       <c r="J237" t="n">
         <v>107.73</v>
       </c>
-      <c r="K237" t="n">
-        <v/>
-      </c>
-      <c r="L237" t="n">
-        <v/>
-      </c>
-      <c r="M237" t="n">
-        <v/>
-      </c>
-      <c r="N237" t="n">
-        <v/>
-      </c>
-      <c r="O237" t="n">
-        <v/>
-      </c>
-      <c r="P237" t="n">
-        <v/>
-      </c>
       <c r="Q237" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-03; 相对D0=1.97%</t>
@@ -16295,24 +12907,12 @@
       <c r="J238" s="4" t="n">
         <v>183.45</v>
       </c>
-      <c r="K238" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L238" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M238" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N238" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O238" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P238" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K238" s="4" t="n"/>
+      <c r="L238" s="4" t="n"/>
+      <c r="M238" s="4" t="n"/>
+      <c r="N238" s="4" t="n"/>
+      <c r="O238" s="4" t="n"/>
+      <c r="P238" s="4" t="n"/>
       <c r="Q238" s="4" t="inlineStr">
         <is>
           <t>D0=163.09; 最新=2026-06-03; 相对D0=12.48%</t>
@@ -16364,24 +12964,6 @@
       <c r="J239" t="n">
         <v>65.45999999999999</v>
       </c>
-      <c r="K239" t="n">
-        <v/>
-      </c>
-      <c r="L239" t="n">
-        <v/>
-      </c>
-      <c r="M239" t="n">
-        <v/>
-      </c>
-      <c r="N239" t="n">
-        <v/>
-      </c>
-      <c r="O239" t="n">
-        <v/>
-      </c>
-      <c r="P239" t="n">
-        <v/>
-      </c>
       <c r="Q239" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-03; 相对D0=1.32%</t>
@@ -16433,24 +13015,12 @@
       <c r="J240" s="4" t="n">
         <v>140.33</v>
       </c>
-      <c r="K240" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L240" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M240" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N240" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O240" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P240" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K240" s="4" t="n"/>
+      <c r="L240" s="4" t="n"/>
+      <c r="M240" s="4" t="n"/>
+      <c r="N240" s="4" t="n"/>
+      <c r="O240" s="4" t="n"/>
+      <c r="P240" s="4" t="n"/>
       <c r="Q240" s="4" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-03; 相对D0=3.39%</t>
@@ -16502,24 +13072,6 @@
       <c r="J241" t="n">
         <v>622.98</v>
       </c>
-      <c r="K241" t="n">
-        <v/>
-      </c>
-      <c r="L241" t="n">
-        <v/>
-      </c>
-      <c r="M241" t="n">
-        <v/>
-      </c>
-      <c r="N241" t="n">
-        <v/>
-      </c>
-      <c r="O241" t="n">
-        <v/>
-      </c>
-      <c r="P241" t="n">
-        <v/>
-      </c>
       <c r="Q241" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-03; 相对D0=3.75%</t>
@@ -16571,24 +13123,12 @@
       <c r="J242" s="4" t="n">
         <v>30.84</v>
       </c>
-      <c r="K242" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L242" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M242" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N242" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O242" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P242" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K242" s="4" t="n"/>
+      <c r="L242" s="4" t="n"/>
+      <c r="M242" s="4" t="n"/>
+      <c r="N242" s="4" t="n"/>
+      <c r="O242" s="4" t="n"/>
+      <c r="P242" s="4" t="n"/>
       <c r="Q242" s="4" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-03; 相对D0=24.05%</t>
@@ -16639,24 +13179,6 @@
       </c>
       <c r="J243" t="n">
         <v>423.7</v>
-      </c>
-      <c r="K243" t="n">
-        <v/>
-      </c>
-      <c r="L243" t="n">
-        <v/>
-      </c>
-      <c r="M243" t="n">
-        <v/>
-      </c>
-      <c r="N243" t="n">
-        <v/>
-      </c>
-      <c r="O243" t="n">
-        <v/>
-      </c>
-      <c r="P243" t="n">
-        <v/>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -16754,7 +13276,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16766,7 +13287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -17037,7 +13558,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -17322,7 +13843,6 @@
       <c r="M11" s="21" t="n">
         <v>0.012782</v>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -17507,7 +14027,6 @@
       <c r="F15" t="n">
         <v>1921.71</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1940.04</v>
       </c>
@@ -17526,7 +14045,6 @@
       <c r="M15" s="21" t="n">
         <v>0.105843</v>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16"/>
     <row r="17">
@@ -17779,9 +14297,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="15" t="n"/>
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17827,9 +14343,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="15" t="n"/>
       <c r="C28" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17875,9 +14389,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="15" t="n"/>
       <c r="C29" s="4" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -17923,9 +14435,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="15" t="n"/>
       <c r="C30" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17975,9 +14485,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="15" t="n"/>
       <c r="C31" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -18023,9 +14531,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="15" t="n"/>
       <c r="C32" s="4" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -18071,9 +14577,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="15" t="n"/>
       <c r="C33" s="4" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -18119,9 +14623,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="15" t="n"/>
       <c r="C34" s="4" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -18167,9 +14669,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -18299,7 +14799,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18311,7 +14810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -18991,7 +15490,6 @@
       <c r="O12" s="22" t="n">
         <v>-0.023456</v>
       </c>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19020,7 +15518,6 @@
       <c r="F13" t="n">
         <v>290.01</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>285</v>
       </c>
@@ -19107,7 +15604,6 @@
       <c r="O14" s="22" t="n">
         <v>-0.027116</v>
       </c>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19136,7 +15632,6 @@
       <c r="F15" t="n">
         <v>67.38</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>66.94</v>
       </c>
@@ -19194,7 +15689,6 @@
       <c r="F16" t="n">
         <v>1069.4399</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1068.04</v>
       </c>
@@ -19219,7 +15713,6 @@
       <c r="O16" s="21" t="n">
         <v>0.007069</v>
       </c>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -19860,9 +16353,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -19914,9 +16405,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -19968,9 +16457,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -20022,9 +16509,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -20134,9 +16619,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20148,7 +16630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -20419,7 +16901,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
@@ -20479,7 +16961,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -20673,7 +17155,6 @@
       <c r="F9" t="n">
         <v>190.96</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>203.7</v>
       </c>
@@ -20704,7 +17185,6 @@
       <c r="Q9" s="21" t="n">
         <v>0.206169</v>
       </c>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20733,7 +17213,6 @@
       <c r="F10" t="n">
         <v>90.87</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>91.09</v>
       </c>
@@ -20896,7 +17375,6 @@
       <c r="Q12" s="21" t="n">
         <v>0.049046</v>
       </c>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -21293,9 +17771,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="15" t="n"/>
       <c r="C26" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -21353,9 +17829,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="15" t="n"/>
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -21458,10 +17932,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21473,7 +17943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:T54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -21908,7 +18378,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
@@ -22050,7 +18520,6 @@
       <c r="F9" t="n">
         <v>105.89</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>104.27</v>
       </c>
@@ -23222,7 +19691,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -23269,7 +19738,6 @@
       <c r="S26" s="21" t="n">
         <v>0.030062</v>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -23292,7 +19760,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -23424,7 +19892,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
@@ -23754,9 +20222,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="15" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -23820,9 +20286,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23886,9 +20350,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B43" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="15" t="n"/>
       <c r="C43" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23952,9 +20414,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="15" t="n"/>
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -24018,9 +20478,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B45" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="15" t="n"/>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -24084,9 +20542,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="15" t="n"/>
       <c r="C46" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -24150,9 +20606,7 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="15" t="n"/>
       <c r="C47" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -24287,8 +20741,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24300,7 +20752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -24461,24 +20913,12 @@
       <c r="J3" s="4" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24530,24 +20970,12 @@
       <c r="J4" s="4" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24599,24 +21027,12 @@
       <c r="J5" s="4" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24668,24 +21084,12 @@
       <c r="J6" s="4" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24737,24 +21141,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24806,24 +21192,12 @@
       <c r="J8" s="4" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24875,24 +21249,12 @@
       <c r="J9" s="4" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24944,24 +21306,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25013,24 +21357,12 @@
       <c r="J11" s="4" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25082,24 +21414,12 @@
       <c r="J12" s="4" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25151,24 +21471,12 @@
       <c r="J13" s="4" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25220,24 +21528,12 @@
       <c r="J14" s="4" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25289,24 +21585,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25358,24 +21636,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25427,24 +21687,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25496,24 +21738,12 @@
       <c r="J18" s="4" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25565,24 +21795,12 @@
       <c r="J19" s="4" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25634,24 +21852,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25703,24 +21903,12 @@
       <c r="J21" s="4" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25957,24 +22145,12 @@
       <c r="J33" s="4" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -26019,11 +22195,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26035,7 +22206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -26208,7 +22379,6 @@
       <c r="F3" t="n">
         <v>22.51</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>22.62</v>
       </c>
@@ -26664,7 +22834,6 @@
       <c r="F9" t="n">
         <v>181.49</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>177.62</v>
       </c>
@@ -27120,7 +23289,6 @@
       <c r="F15" t="n">
         <v>16.12</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>15.47</v>
       </c>
@@ -27272,7 +23440,6 @@
       <c r="F17" t="n">
         <v>610.26</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>612.34</v>
       </c>
@@ -27648,7 +23815,6 @@
       <c r="F22" t="n">
         <v>141.22</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>136.2</v>
       </c>
@@ -27724,7 +23890,6 @@
       <c r="F23" t="n">
         <v>58.81</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>57.46</v>
       </c>
@@ -27800,7 +23965,6 @@
       <c r="F24" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>84.64</v>
       </c>
@@ -27870,7 +24034,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
@@ -27952,7 +24116,6 @@
       <c r="F26" t="n">
         <v>426.01</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>433.59</v>
       </c>
@@ -27995,7 +24158,6 @@
       <c r="U26" s="22" t="n">
         <v>-0.005422</v>
       </c>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -28018,7 +24180,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -28322,7 +24484,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
@@ -28398,7 +24560,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
@@ -28812,9 +24974,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B45" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="15" t="n"/>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -28916,11 +25076,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29228,7 +25383,6 @@
       <c r="V3" t="n">
         <v>205.7700042724609</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.96; 4H分金=50.57</t>
@@ -29406,7 +25560,6 @@
       <c r="V5" t="n">
         <v>275.4400024414062</v>
       </c>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.55; 4H分金=47.87</t>
@@ -29488,8 +25641,6 @@
       <c r="T6" t="b">
         <v>0</v>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
         <v>84</v>
       </c>
@@ -29580,7 +25731,6 @@
       <c r="V7" t="n">
         <v>50.72499847412109</v>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=50.72; Gann0=35.68; 段涨幅=42.17%</t>
@@ -29668,7 +25818,6 @@
       <c r="V8" t="n">
         <v>50.72499847412109</v>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.23; 4H分金=31.82</t>
@@ -29750,8 +25899,6 @@
       <c r="T9" t="b">
         <v>0</v>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
         <v>87</v>
       </c>
@@ -29932,7 +26079,6 @@
       <c r="V11" t="n">
         <v>16.90999984741211</v>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.49; 4H分金=48.89</t>
@@ -30020,7 +26166,6 @@
       <c r="V12" t="n">
         <v>245.9499969482422</v>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=245.95; Gann0=148.95; 段涨幅=65.13%</t>
@@ -30108,7 +26253,6 @@
       <c r="V13" t="n">
         <v>211.3399963378906</v>
       </c>
-      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.35; 4H分金=46.23</t>
@@ -30196,7 +26340,6 @@
       <c r="V14" t="n">
         <v>132.1499938964844</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=132.15; Gann0=94.82; 段涨幅=39.37%</t>
@@ -30284,7 +26427,6 @@
       <c r="V15" t="n">
         <v>132.1499938964844</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.22; 4H分金=42.31</t>
@@ -30372,7 +26514,6 @@
       <c r="V16" t="n">
         <v>49.34000015258789</v>
       </c>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.15; 4H分金=46.01</t>
@@ -30460,7 +26601,6 @@
       <c r="V17" t="n">
         <v>278.7049865722656</v>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=62.15; 4H分金=49.39</t>
@@ -30542,8 +26682,6 @@
       <c r="T18" t="b">
         <v>0</v>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
         <v>86</v>
       </c>
@@ -30634,7 +26772,6 @@
       <c r="V19" t="n">
         <v>9.689999580383301</v>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=9.69; Gann0=6.73; 段涨幅=43.98%</t>
@@ -30722,7 +26859,6 @@
       <c r="V20" t="n">
         <v>9.689999580383301</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.03; 4H分金=36.11</t>
@@ -30900,7 +27036,6 @@
       <c r="V22" t="n">
         <v>94.40000152587891</v>
       </c>
-      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-29; 1出价格=94.40; Gann0=73.18; 段涨幅=29.00%</t>
@@ -30988,7 +27123,6 @@
       <c r="V23" t="n">
         <v>94.40000152587891</v>
       </c>
-      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.04; 4H分金=38.45</t>
@@ -31076,7 +27210,6 @@
       <c r="V24" t="n">
         <v>108.0599975585938</v>
       </c>
-      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=57.73; 4H分金=46.87</t>
@@ -31158,8 +27291,6 @@
       <c r="T25" t="b">
         <v>0</v>
       </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
         <v>86</v>
       </c>
@@ -31250,7 +27381,6 @@
       <c r="V26" t="n">
         <v>204.8000030517578</v>
       </c>
-      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=45.47; 4H分金=39.27</t>
@@ -31692,8 +27822,6 @@
       <c r="T31" t="b">
         <v>0</v>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="n">
         <v>87</v>
       </c>
@@ -31874,7 +28002,6 @@
       <c r="V33" t="n">
         <v>466.3200073242188</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-01; 1出价格=466.32; Gann0=409.58; 段涨幅=13.85%</t>
@@ -31962,7 +28089,6 @@
       <c r="V34" t="n">
         <v>466.3200073242188</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.36; 4H分金=39.33</t>
@@ -32050,7 +28176,6 @@
       <c r="V35" t="n">
         <v>31.59000015258789</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=31.59; Gann0=21.72; 段涨幅=45.46%</t>
@@ -32138,7 +28263,6 @@
       <c r="V36" t="n">
         <v>31.59000015258789</v>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.12; 4H分金=35.70</t>
@@ -32226,7 +28350,6 @@
       <c r="V37" t="n">
         <v>139.1999969482422</v>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=57.15; 4H分金=45.15</t>
@@ -32308,8 +28431,6 @@
       <c r="T38" t="b">
         <v>0</v>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
         <v>91</v>
       </c>
@@ -32400,7 +28521,6 @@
       <c r="V39" t="n">
         <v>232.2799987792969</v>
       </c>
-      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.20; 4H分金=39.00</t>
@@ -32668,7 +28788,6 @@
       <c r="V42" t="n">
         <v>163.1300048828125</v>
       </c>
-      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=57.33; 4H分金=54.37</t>
@@ -32756,7 +28875,6 @@
       <c r="V43" t="n">
         <v>73.86000061035156</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=73.86; Gann0=53.96; 段涨幅=36.89%</t>
@@ -32844,7 +28962,6 @@
       <c r="V44" t="n">
         <v>302.9500122070312</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=62.43; 4H分金=51.45</t>
@@ -32932,7 +29049,6 @@
       <c r="V45" t="n">
         <v>163.6999969482422</v>
       </c>
-      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-01; 1出价格=163.70; Gann0=131.63; 段涨幅=24.36%</t>
@@ -33020,7 +29136,6 @@
       <c r="V46" t="n">
         <v>163.6999969482422</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.05; 4H分金=35.90</t>
@@ -33108,7 +29223,6 @@
       <c r="V47" t="n">
         <v>112.2099990844727</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.86; 4H分金=46.66</t>
@@ -33196,7 +29310,6 @@
       <c r="V48" t="n">
         <v>16.76000022888184</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-29; 1出价格=16.76; Gann0=12.71; 段涨幅=31.86%</t>
@@ -33284,7 +29397,6 @@
       <c r="V49" t="n">
         <v>14.30000019073486</v>
       </c>
-      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=14.30; Gann0=9.66; 段涨幅=47.96%</t>
@@ -33372,7 +29484,6 @@
       <c r="V50" t="n">
         <v>14.30000019073486</v>
       </c>
-      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.81; 4H分金=42.04</t>
@@ -33460,7 +29571,6 @@
       <c r="V51" t="n">
         <v>284.989990234375</v>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=63.55; 4H分金=49.60</t>
@@ -33632,8 +29742,6 @@
       <c r="T53" t="b">
         <v>0</v>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="n">
         <v>91</v>
       </c>
@@ -33724,7 +29832,6 @@
       <c r="V54" t="n">
         <v>18.79500007629395</v>
       </c>
-      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-01; 1出价格=18.80; Gann0=14.92; 段涨幅=25.97%</t>
@@ -33812,7 +29919,6 @@
       <c r="V55" t="n">
         <v>18.79500007629395</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.40; 4H分金=35.80</t>
@@ -33900,7 +30006,6 @@
       <c r="V56" t="n">
         <v>75.59999847412109</v>
       </c>
-      <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=57.70; 4H分金=46.72</t>
@@ -33988,7 +30093,6 @@
       <c r="V57" t="n">
         <v>119.379997253418</v>
       </c>
-      <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.70; 4H分金=46.62</t>
@@ -34166,7 +30270,6 @@
       <c r="V59" t="n">
         <v>15.48999977111816</v>
       </c>
-      <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.76; 4H分金=48.75</t>
@@ -34248,8 +30351,6 @@
       <c r="T60" t="b">
         <v>0</v>
       </c>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
       <c r="W60" t="n">
         <v>91</v>
       </c>
@@ -34340,7 +30441,6 @@
       <c r="V61" t="n">
         <v>167.3999938964844</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=167.40; Gann0=132.66; 段涨幅=26.19%</t>
@@ -34376,7 +30476,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -34643,7 +30743,6 @@
       <c r="D3" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="8" t="n">
         <v>46175</v>
       </c>
@@ -34749,7 +30848,6 @@
       <c r="D5" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="8" t="n">
         <v>46174</v>
       </c>
@@ -34909,7 +31007,6 @@
       <c r="D8" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="8" t="n">
         <v>46164</v>
       </c>
@@ -34961,7 +31058,6 @@
       <c r="D9" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="8" t="n">
         <v>46168</v>
       </c>
@@ -35013,7 +31109,6 @@
       <c r="D10" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="8" t="n">
         <v>46174</v>
       </c>
@@ -35065,7 +31160,6 @@
       <c r="D11" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="8" t="n">
         <v>46175</v>
       </c>
@@ -35171,7 +31265,6 @@
       <c r="D13" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="8" t="n">
         <v>46174</v>
       </c>
@@ -35223,7 +31316,6 @@
       <c r="D14" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="8" t="n">
         <v>46168</v>
       </c>
@@ -35329,7 +31421,6 @@
       <c r="D16" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="8" t="n">
         <v>46164</v>
       </c>
@@ -35381,7 +31472,6 @@
       <c r="D17" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="8" t="n">
         <v>46175</v>
       </c>
@@ -35430,7 +31520,6 @@
           <t>19 COWOS</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" s="8" t="n">
         <v>46164</v>
       </c>
@@ -35539,7 +31628,6 @@
       <c r="D20" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="8" t="n">
         <v>46164</v>
       </c>
@@ -35699,7 +31787,6 @@
       <c r="D23" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="8" t="n">
         <v>46164</v>
       </c>
@@ -36532,7 +32619,6 @@
       <c r="I13" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" s="8" t="n">
         <v>46175</v>
       </c>
@@ -37214,7 +33300,6 @@
       <c r="I25" t="n">
         <v>4</v>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" s="8" t="n">
         <v>46171</v>
       </c>
@@ -37326,7 +33411,6 @@
       <c r="I27" t="n">
         <v>6</v>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" s="8" t="n">
         <v>46169</v>
       </c>
@@ -37358,7 +33442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -37707,8 +33791,6 @@
       <c r="F11" t="n">
         <v>43.71</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -37771,8 +33853,6 @@
       <c r="F13" t="n">
         <v>282.27</v>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -37870,7 +33950,6 @@
           <t>2026-05-22 (92), 2026-05-27 (92), 2026-06-01 (88)</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37904,7 +33983,6 @@
           <t>2026-06-02 (88)</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -37968,7 +34046,6 @@
           <t>2026-05-22 (92)</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -38002,7 +34079,6 @@
           <t>2026-06-02 (83)</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -38025,7 +34101,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
@@ -38104,7 +34180,6 @@
           <t>2026-06-02 (92)</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24"/>
     <row r="25">
@@ -38316,9 +34391,7 @@
           <t>APLD</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -38346,9 +34419,7 @@
           <t>CPNG</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>23 杂项</t>
@@ -38376,9 +34447,7 @@
           <t>CRDO</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -38406,9 +34475,7 @@
           <t>CRWV</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -38436,9 +34503,7 @@
           <t>EOSE</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="16" t="n"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -38457,8 +34522,6 @@
       <c r="F39" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -38466,9 +34529,7 @@
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="15" t="n"/>
       <c r="C40" s="4" t="inlineStr">
         <is>
           <t>16 金融股</t>
@@ -38496,9 +34557,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="16" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -38517,8 +34576,6 @@
       <c r="F41" t="n">
         <v>427.34</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -38526,9 +34583,7 @@
           <t>NNE</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -38556,9 +34611,7 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="B43" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="15" t="n"/>
       <c r="C43" s="4" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -38586,9 +34639,7 @@
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="16" t="n"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -38607,8 +34658,6 @@
       <c r="F44" t="n">
         <v>142.2</v>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -38616,9 +34665,7 @@
           <t>RUN</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="16" t="n"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>10 太阳能</t>
@@ -38637,8 +34684,6 @@
       <c r="F45" t="n">
         <v>14.85</v>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -38646,9 +34691,7 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="15" t="n"/>
       <c r="C46" s="4" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -38676,9 +34719,7 @@
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="15" t="n"/>
       <c r="C47" s="4" t="inlineStr">
         <is>
           <t>16 金融股</t>
@@ -38706,9 +34747,7 @@
           <t>VST</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B48" s="16" t="n"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -38727,8 +34766,6 @@
       <c r="F48" t="n">
         <v>153.8</v>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49"/>
     <row r="50">
@@ -38820,7 +34857,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39064,7 +35100,6 @@
       <c r="I6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -39167,7 +35202,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
@@ -39207,7 +35242,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F10" s="10" t="n">
@@ -39247,7 +35282,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F11" s="10" t="n">
@@ -40084,7 +36119,6 @@
       <c r="I32" s="21" t="n">
         <v>0.002135</v>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -40200,7 +36234,6 @@
       <c r="I35" s="21" t="n">
         <v>0.007031</v>
       </c>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -40240,7 +36273,6 @@
       <c r="I36" s="22" t="n">
         <v>-0.009039999999999999</v>
       </c>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -40345,7 +36377,6 @@
       <c r="F39" t="n">
         <v>315.2</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>310.26</v>
       </c>
@@ -40385,14 +36416,12 @@
       <c r="F40" t="n">
         <v>72.33</v>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>69.02</v>
       </c>
       <c r="I40" s="22" t="n">
         <v>-0.045763</v>
       </c>
-      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -40421,14 +36450,12 @@
       <c r="F41" t="n">
         <v>11.72</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>11.1</v>
       </c>
       <c r="I41" s="22" t="n">
         <v>-0.052901</v>
       </c>
-      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42"/>
     <row r="43">
@@ -40658,7 +36685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -40765,7 +36792,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
@@ -40989,7 +37016,6 @@
       <c r="F8" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>68.5</v>
       </c>
@@ -41123,7 +37149,6 @@
       <c r="F11" t="n">
         <v>14.7</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>14.68</v>
       </c>
@@ -41136,7 +37161,6 @@
       <c r="K11" s="21" t="n">
         <v>0.00068</v>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -41257,7 +37281,6 @@
       <c r="F14" t="n">
         <v>15.58</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>15.25</v>
       </c>
@@ -41270,7 +37293,6 @@
       <c r="K14" s="22" t="n">
         <v>-0.046855</v>
       </c>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -41408,7 +37430,6 @@
       <c r="K17" s="21" t="n">
         <v>0.024893</v>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -41965,9 +37986,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -42007,9 +38026,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -42053,9 +38070,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -42095,9 +38110,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B39" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="15" t="n"/>
       <c r="C39" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -42137,9 +38150,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="15" t="n"/>
       <c r="C40" s="4" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -42179,9 +38190,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="15" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -42221,9 +38230,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -42347,7 +38354,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
